--- a/Daily_Practice/Day16_(2).xlsx
+++ b/Daily_Practice/Day16_(2).xlsx
@@ -5,54 +5,64 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS journey\Old\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS journey\learning-excel-data-analysis\Daily_Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF217D00-8F60-4D1B-942C-29BA8FDB41EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822263F4-58BE-413E-90EE-364C09B7142E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Forcasting" sheetId="7" r:id="rId1"/>
     <sheet name="Forecasting Data" sheetId="6" r:id="rId2"/>
-    <sheet name="Answer Report 1" sheetId="13" r:id="rId3"/>
-    <sheet name="What if Analysis" sheetId="8" r:id="rId4"/>
-    <sheet name="Scenario Summary" sheetId="12" r:id="rId5"/>
+    <sheet name="What if Analysis" sheetId="8" r:id="rId3"/>
+    <sheet name="Answer Report 2(Constraint)" sheetId="19" r:id="rId4"/>
+    <sheet name="Answer Report 1(NoConstraints)" sheetId="14" r:id="rId5"/>
+    <sheet name="Scenario Summary" sheetId="12" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="base" localSheetId="3">'What if Analysis'!$B$2</definedName>
+    <definedName name="base" localSheetId="2">'What if Analysis'!$B$2</definedName>
     <definedName name="base2">'What if Analysis'!$J$2</definedName>
-    <definedName name="bonus" localSheetId="3">'What if Analysis'!$B$3</definedName>
+    <definedName name="base3">'What if Analysis'!$B$16</definedName>
+    <definedName name="bonus" localSheetId="2">'What if Analysis'!$B$3</definedName>
     <definedName name="bonus2">'What if Analysis'!$J$3</definedName>
-    <definedName name="raise" localSheetId="3">'What if Analysis'!$B$4</definedName>
+    <definedName name="bonus3">'What if Analysis'!$B$17</definedName>
+    <definedName name="raise" localSheetId="2">'What if Analysis'!$B$4</definedName>
     <definedName name="raise2">'What if Analysis'!$J$4</definedName>
-    <definedName name="solver_adj" localSheetId="3" hidden="1">'What if Analysis'!$J$3:$J$4</definedName>
-    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
-    <definedName name="solver_drv" localSheetId="3" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
-    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
-    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
-    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
-    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
-    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="3" hidden="1">0</definedName>
-    <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="3" hidden="1">'What if Analysis'!$J$2</definedName>
-    <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
-    <definedName name="solver_rbv" localSheetId="3" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
-    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
-    <definedName name="solver_scl" localSheetId="3" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
-    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
-    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
-    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
-    <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
-    <definedName name="solver_val" localSheetId="3" hidden="1">640000</definedName>
-    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
+    <definedName name="raise3">'What if Analysis'!$B$18</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'What if Analysis'!$B$17:$B$18</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'What if Analysis'!$B$17</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'What if Analysis'!$B$18</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'What if Analysis'!$B$27</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">0.11</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">0.1</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">640000</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
     <definedName name="Total">'What if Analysis'!$B$13</definedName>
     <definedName name="Year_0">'What if Analysis'!$B$8</definedName>
     <definedName name="Year_1">'What if Analysis'!$B$9</definedName>
@@ -78,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="84">
   <si>
     <t>Slack</t>
   </si>
@@ -201,9 +211,6 @@
     <t>Worksheet: [Day16_(2).xlsx]What if Analysis</t>
   </si>
   <si>
-    <t>Report Created: 04-10-2026 22:55:34</t>
-  </si>
-  <si>
     <t>Result: Solver found a solution.  All Constraints and optimality conditions are satisfied.</t>
   </si>
   <si>
@@ -211,12 +218,6 @@
   </si>
   <si>
     <t>Engine: GRG Nonlinear</t>
-  </si>
-  <si>
-    <t>Solution Time: 0.031 Seconds.</t>
-  </si>
-  <si>
-    <t>Iterations: 0 Subproblems: 0</t>
   </si>
   <si>
     <t>Solver Options</t>
@@ -290,17 +291,69 @@
   <si>
     <t>Binding</t>
   </si>
+  <si>
+    <t>Report Created: 05-10-2026 08:56:05</t>
+  </si>
+  <si>
+    <t>Solution Time: 0.062 Seconds.</t>
+  </si>
+  <si>
+    <t>Iterations: 2 Subproblems: 0</t>
+  </si>
+  <si>
+    <t>(One Variable change)</t>
+  </si>
+  <si>
+    <t>(Two or more variable change)</t>
+  </si>
+  <si>
+    <t>Solver with Constrains</t>
+  </si>
+  <si>
+    <t>$B$27</t>
+  </si>
+  <si>
+    <t>$B$17</t>
+  </si>
+  <si>
+    <t>bonus3</t>
+  </si>
+  <si>
+    <t>$B$18</t>
+  </si>
+  <si>
+    <t>raise3</t>
+  </si>
+  <si>
+    <t>$B$27=640000</t>
+  </si>
+  <si>
+    <t>Not Binding</t>
+  </si>
+  <si>
+    <t>Report Created: 05-10-2026 18:02:20</t>
+  </si>
+  <si>
+    <t>Solution Time: 0.079 Seconds.</t>
+  </si>
+  <si>
+    <t>$B$17&lt;=0.11</t>
+  </si>
+  <si>
+    <t>$B$18&lt;=0.1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="[$-409]d\-mmm;@"/>
-    <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="_(&quot;₹&quot;* #,##0_);_(&quot;₹&quot;* \(#,##0\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm;@"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="168" formatCode="_(&quot;₹&quot;* #,##0_);_(&quot;₹&quot;* \(#,##0\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -385,7 +438,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,8 +492,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -874,29 +933,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -917,7 +991,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -930,7 +1004,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -938,7 +1012,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -948,28 +1022,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -984,45 +1057,67 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1037,7 +1132,7 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="[$-409]d\-mmm;@"/>
+      <numFmt numFmtId="164" formatCode="[$-409]d\-mmm;@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1122,7 +1217,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -12624,15 +12719,15 @@
         <v>45292</v>
       </c>
       <c r="C367">
-        <f>_xlfn.FORECAST.ETS(A367,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" ref="C367:C398" si="0">_xlfn.FORECAST.ETS(A367,$B$2:$B$366,$A$2:$A$366,1,1)</f>
         <v>44.490739333500457</v>
       </c>
       <c r="D367" s="10">
-        <f>C367-_xlfn.FORECAST.ETS.CONFINT(A367,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="D367:D398" si="1">C367-_xlfn.FORECAST.ETS.CONFINT(A367,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>-2.1006233086081778</v>
       </c>
       <c r="E367" s="10">
-        <f>C367+_xlfn.FORECAST.ETS.CONFINT(A367,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="E367:E398" si="2">C367+_xlfn.FORECAST.ETS.CONFINT(A367,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>91.082101975609092</v>
       </c>
     </row>
@@ -12641,15 +12736,15 @@
         <v>45293</v>
       </c>
       <c r="C368">
-        <f>_xlfn.FORECAST.ETS(A368,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>60.561481890528384</v>
       </c>
       <c r="D368" s="10">
-        <f>C368-_xlfn.FORECAST.ETS.CONFINT(A368,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>12.513519363542436</v>
       </c>
       <c r="E368" s="10">
-        <f>C368+_xlfn.FORECAST.ETS.CONFINT(A368,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>108.60944441751434</v>
       </c>
     </row>
@@ -12658,15 +12753,15 @@
         <v>45294</v>
       </c>
       <c r="C369">
-        <f>_xlfn.FORECAST.ETS(A369,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>79.425063879258175</v>
       </c>
       <c r="D369" s="10">
-        <f>C369-_xlfn.FORECAST.ETS.CONFINT(A369,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>29.952297992837352</v>
       </c>
       <c r="E369" s="10">
-        <f>C369+_xlfn.FORECAST.ETS.CONFINT(A369,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>128.89782976567901</v>
       </c>
     </row>
@@ -12675,15 +12770,15 @@
         <v>45295</v>
       </c>
       <c r="C370">
-        <f>_xlfn.FORECAST.ETS(A370,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>63.135902609367555</v>
       </c>
       <c r="D370" s="10">
-        <f>C370-_xlfn.FORECAST.ETS.CONFINT(A370,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>12.267415323696312</v>
       </c>
       <c r="E370" s="10">
-        <f>C370+_xlfn.FORECAST.ETS.CONFINT(A370,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>114.0043898950388</v>
       </c>
     </row>
@@ -12692,15 +12787,15 @@
         <v>45296</v>
       </c>
       <c r="C371">
-        <f>_xlfn.FORECAST.ETS(A371,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>68.609720435612303</v>
       </c>
       <c r="D371" s="10">
-        <f>C371-_xlfn.FORECAST.ETS.CONFINT(A371,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>16.372220999436486</v>
       </c>
       <c r="E371" s="10">
-        <f>C371+_xlfn.FORECAST.ETS.CONFINT(A371,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>120.84721987178813</v>
       </c>
     </row>
@@ -12709,15 +12804,15 @@
         <v>45297</v>
       </c>
       <c r="C372">
-        <f>_xlfn.FORECAST.ETS(A372,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>34.607091016174465</v>
       </c>
       <c r="D372" s="10">
-        <f>C372-_xlfn.FORECAST.ETS.CONFINT(A372,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-18.974799131511318</v>
       </c>
       <c r="E372" s="10">
-        <f>C372+_xlfn.FORECAST.ETS.CONFINT(A372,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>88.188981163860248</v>
       </c>
     </row>
@@ -12726,15 +12821,15 @@
         <v>45298</v>
       </c>
       <c r="C373">
-        <f>_xlfn.FORECAST.ETS(A373,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>29.526809189014482</v>
       </c>
       <c r="D373" s="10">
-        <f>C373-_xlfn.FORECAST.ETS.CONFINT(A373,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-25.376698473112494</v>
       </c>
       <c r="E373" s="10">
-        <f>C373+_xlfn.FORECAST.ETS.CONFINT(A373,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>84.430316851141455</v>
       </c>
     </row>
@@ -12743,15 +12838,15 @@
         <v>45299</v>
       </c>
       <c r="C374">
-        <f>_xlfn.FORECAST.ETS(A374,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>44.017548522514943</v>
       </c>
       <c r="D374" s="10">
-        <f>C374-_xlfn.FORECAST.ETS.CONFINT(A374,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-15.770317225685204</v>
       </c>
       <c r="E374" s="10">
-        <f>C374+_xlfn.FORECAST.ETS.CONFINT(A374,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>103.80541427071509</v>
       </c>
     </row>
@@ -12760,15 +12855,15 @@
         <v>45300</v>
       </c>
       <c r="C375">
-        <f>_xlfn.FORECAST.ETS(A375,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>60.088291079542856</v>
       </c>
       <c r="D375" s="10">
-        <f>C375-_xlfn.FORECAST.ETS.CONFINT(A375,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-0.90519473465334954</v>
       </c>
       <c r="E375" s="10">
-        <f>C375+_xlfn.FORECAST.ETS.CONFINT(A375,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>121.08177689373906</v>
       </c>
     </row>
@@ -12777,15 +12872,15 @@
         <v>45301</v>
       </c>
       <c r="C376">
-        <f>_xlfn.FORECAST.ETS(A376,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>78.951873068272647</v>
       </c>
       <c r="D376" s="10">
-        <f>C376-_xlfn.FORECAST.ETS.CONFINT(A376,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>16.76708107946633</v>
       </c>
       <c r="E376" s="10">
-        <f>C376+_xlfn.FORECAST.ETS.CONFINT(A376,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>141.13666505707897</v>
       </c>
     </row>
@@ -12794,15 +12889,15 @@
         <v>45302</v>
       </c>
       <c r="C377">
-        <f>_xlfn.FORECAST.ETS(A377,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>62.662711798382027</v>
       </c>
       <c r="D377" s="10">
-        <f>C377-_xlfn.FORECAST.ETS.CONFINT(A377,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-0.69991410213302174</v>
       </c>
       <c r="E377" s="10">
-        <f>C377+_xlfn.FORECAST.ETS.CONFINT(A377,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>126.02533769889708</v>
       </c>
     </row>
@@ -12811,15 +12906,15 @@
         <v>45303</v>
       </c>
       <c r="C378">
-        <f>_xlfn.FORECAST.ETS(A378,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>68.136529624626775</v>
       </c>
       <c r="D378" s="10">
-        <f>C378-_xlfn.FORECAST.ETS.CONFINT(A378,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>3.6087706969433242</v>
       </c>
       <c r="E378" s="10">
-        <f>C378+_xlfn.FORECAST.ETS.CONFINT(A378,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>132.66428855231021</v>
       </c>
     </row>
@@ -12828,15 +12923,15 @@
         <v>45304</v>
       </c>
       <c r="C379">
-        <f>_xlfn.FORECAST.ETS(A379,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>34.133900205188944</v>
       </c>
       <c r="D379" s="10">
-        <f>C379-_xlfn.FORECAST.ETS.CONFINT(A379,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-31.546999833278015</v>
       </c>
       <c r="E379" s="10">
-        <f>C379+_xlfn.FORECAST.ETS.CONFINT(A379,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>99.814800243655895</v>
       </c>
     </row>
@@ -12845,15 +12940,15 @@
         <v>45305</v>
       </c>
       <c r="C380">
-        <f>_xlfn.FORECAST.ETS(A380,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>29.053618378028954</v>
       </c>
       <c r="D380" s="10">
-        <f>C380-_xlfn.FORECAST.ETS.CONFINT(A380,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-37.769084166991888</v>
       </c>
       <c r="E380" s="10">
-        <f>C380+_xlfn.FORECAST.ETS.CONFINT(A380,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>95.876320923049803</v>
       </c>
     </row>
@@ -12862,15 +12957,15 @@
         <v>45306</v>
       </c>
       <c r="C381">
-        <f>_xlfn.FORECAST.ETS(A381,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>43.544357711529415</v>
       </c>
       <c r="D381" s="10">
-        <f>C381-_xlfn.FORECAST.ETS.CONFINT(A381,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-27.455727426564422</v>
       </c>
       <c r="E381" s="10">
-        <f>C381+_xlfn.FORECAST.ETS.CONFINT(A381,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>114.54444284962325</v>
       </c>
     </row>
@@ -12879,15 +12974,15 @@
         <v>45307</v>
       </c>
       <c r="C382">
-        <f>_xlfn.FORECAST.ETS(A382,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>59.615100268557327</v>
       </c>
       <c r="D382" s="10">
-        <f>C382-_xlfn.FORECAST.ETS.CONFINT(A382,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-12.458515122590086</v>
       </c>
       <c r="E382" s="10">
-        <f>C382+_xlfn.FORECAST.ETS.CONFINT(A382,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>131.68871565970474</v>
       </c>
     </row>
@@ -12896,15 +12991,15 @@
         <v>45308</v>
       </c>
       <c r="C383">
-        <f>_xlfn.FORECAST.ETS(A383,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>78.478682257287119</v>
       </c>
       <c r="D383" s="10">
-        <f>C383-_xlfn.FORECAST.ETS.CONFINT(A383,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>5.339383696668321</v>
       </c>
       <c r="E383" s="10">
-        <f>C383+_xlfn.FORECAST.ETS.CONFINT(A383,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>151.6179808179059</v>
       </c>
     </row>
@@ -12913,15 +13008,15 @@
         <v>45309</v>
       </c>
       <c r="C384">
-        <f>_xlfn.FORECAST.ETS(A384,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>62.189520987396506</v>
       </c>
       <c r="D384" s="10">
-        <f>C384-_xlfn.FORECAST.ETS.CONFINT(A384,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-12.007981034515282</v>
       </c>
       <c r="E384" s="10">
-        <f>C384+_xlfn.FORECAST.ETS.CONFINT(A384,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>136.38702300930828</v>
       </c>
     </row>
@@ -12930,15 +13025,15 @@
         <v>45310</v>
       </c>
       <c r="C385">
-        <f>_xlfn.FORECAST.ETS(A385,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>67.663338813641246</v>
       </c>
       <c r="D385" s="10">
-        <f>C385-_xlfn.FORECAST.ETS.CONFINT(A385,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-7.585231366249829</v>
       </c>
       <c r="E385" s="10">
-        <f>C385+_xlfn.FORECAST.ETS.CONFINT(A385,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>142.91190899353234</v>
       </c>
     </row>
@@ -12947,15 +13042,15 @@
         <v>45311</v>
       </c>
       <c r="C386">
-        <f>_xlfn.FORECAST.ETS(A386,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>33.660709394203423</v>
       </c>
       <c r="D386" s="10">
-        <f>C386-_xlfn.FORECAST.ETS.CONFINT(A386,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-42.632116998116373</v>
       </c>
       <c r="E386" s="10">
-        <f>C386+_xlfn.FORECAST.ETS.CONFINT(A386,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>109.95353578652322</v>
       </c>
     </row>
@@ -12964,15 +13059,15 @@
         <v>45312</v>
       </c>
       <c r="C387">
-        <f>_xlfn.FORECAST.ETS(A387,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>28.580427567043433</v>
       </c>
       <c r="D387" s="10">
-        <f>C387-_xlfn.FORECAST.ETS.CONFINT(A387,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-48.750147125206936</v>
       </c>
       <c r="E387" s="10">
-        <f>C387+_xlfn.FORECAST.ETS.CONFINT(A387,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>105.9110022592938</v>
       </c>
     </row>
@@ -12981,15 +13076,15 @@
         <v>45313</v>
       </c>
       <c r="C388">
-        <f>_xlfn.FORECAST.ETS(A388,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>43.071166900543886</v>
       </c>
       <c r="D388" s="10">
-        <f>C388-_xlfn.FORECAST.ETS.CONFINT(A388,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-37.993707166488107</v>
       </c>
       <c r="E388" s="10">
-        <f>C388+_xlfn.FORECAST.ETS.CONFINT(A388,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>124.13604096757588</v>
       </c>
     </row>
@@ -12998,15 +13093,15 @@
         <v>45314</v>
       </c>
       <c r="C389">
-        <f>_xlfn.FORECAST.ETS(A389,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>59.141909457571813</v>
       </c>
       <c r="D389" s="10">
-        <f>C389-_xlfn.FORECAST.ETS.CONFINT(A389,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-22.914766153423287</v>
       </c>
       <c r="E389" s="10">
-        <f>C389+_xlfn.FORECAST.ETS.CONFINT(A389,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>141.1985850685669</v>
       </c>
     </row>
@@ -13015,15 +13110,15 @@
         <v>45315</v>
       </c>
       <c r="C390">
-        <f>_xlfn.FORECAST.ETS(A390,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>78.005491446301605</v>
       </c>
       <c r="D390" s="10">
-        <f>C390-_xlfn.FORECAST.ETS.CONFINT(A390,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-5.0382898993070029</v>
       </c>
       <c r="E390" s="10">
-        <f>C390+_xlfn.FORECAST.ETS.CONFINT(A390,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>161.0492727919102</v>
       </c>
     </row>
@@ -13032,15 +13127,15 @@
         <v>45316</v>
       </c>
       <c r="C391">
-        <f>_xlfn.FORECAST.ETS(A391,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>61.716330176410985</v>
       </c>
       <c r="D391" s="10">
-        <f>C391-_xlfn.FORECAST.ETS.CONFINT(A391,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-22.310052421921888</v>
       </c>
       <c r="E391" s="10">
-        <f>C391+_xlfn.FORECAST.ETS.CONFINT(A391,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>145.74271277474386</v>
       </c>
     </row>
@@ -13049,15 +13144,15 @@
         <v>45317</v>
       </c>
       <c r="C392">
-        <f>_xlfn.FORECAST.ETS(A392,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>67.190148002655718</v>
       </c>
       <c r="D392" s="10">
-        <f>C392-_xlfn.FORECAST.ETS.CONFINT(A392,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-17.814513110666326</v>
       </c>
       <c r="E392" s="10">
-        <f>C392+_xlfn.FORECAST.ETS.CONFINT(A392,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>152.19480911597776</v>
       </c>
     </row>
@@ -13066,15 +13161,15 @@
         <v>45318</v>
       </c>
       <c r="C393">
-        <f>_xlfn.FORECAST.ETS(A393,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>33.187518583217894</v>
       </c>
       <c r="D393" s="10">
-        <f>C393-_xlfn.FORECAST.ETS.CONFINT(A393,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-52.791271109213312</v>
       </c>
       <c r="E393" s="10">
-        <f>C393+_xlfn.FORECAST.ETS.CONFINT(A393,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>119.1663082756491</v>
       </c>
     </row>
@@ -13083,15 +13178,15 @@
         <v>45319</v>
       </c>
       <c r="C394">
-        <f>_xlfn.FORECAST.ETS(A394,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>28.107236756057912</v>
       </c>
       <c r="D394" s="10">
-        <f>C394-_xlfn.FORECAST.ETS.CONFINT(A394,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-58.841696026497473</v>
       </c>
       <c r="E394" s="10">
-        <f>C394+_xlfn.FORECAST.ETS.CONFINT(A394,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>115.0561695386133</v>
       </c>
     </row>
@@ -13100,15 +13195,15 @@
         <v>45320</v>
       </c>
       <c r="C395">
-        <f>_xlfn.FORECAST.ETS(A395,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>42.597976089558372</v>
       </c>
       <c r="D395" s="10">
-        <f>C395-_xlfn.FORECAST.ETS.CONFINT(A395,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-47.776706108313434</v>
       </c>
       <c r="E395" s="10">
-        <f>C395+_xlfn.FORECAST.ETS.CONFINT(A395,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>132.97265828743019</v>
       </c>
     </row>
@@ -13117,15 +13212,15 @@
         <v>45321</v>
       </c>
       <c r="C396">
-        <f>_xlfn.FORECAST.ETS(A396,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>58.668718646586285</v>
       </c>
       <c r="D396" s="10">
-        <f>C396-_xlfn.FORECAST.ETS.CONFINT(A396,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-32.642673742740726</v>
       </c>
       <c r="E396" s="10">
-        <f>C396+_xlfn.FORECAST.ETS.CONFINT(A396,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>149.9801110359133</v>
       </c>
     </row>
@@ -13134,15 +13229,15 @@
         <v>45322</v>
       </c>
       <c r="C397">
-        <f>_xlfn.FORECAST.ETS(A397,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>77.532300635316076</v>
       </c>
       <c r="D397" s="10">
-        <f>C397-_xlfn.FORECAST.ETS.CONFINT(A397,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-14.71289095419084</v>
       </c>
       <c r="E397" s="10">
-        <f>C397+_xlfn.FORECAST.ETS.CONFINT(A397,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>169.77749222482299</v>
       </c>
     </row>
@@ -13151,15 +13246,15 @@
         <v>45323</v>
       </c>
       <c r="C398">
-        <f>_xlfn.FORECAST.ETS(A398,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="0"/>
         <v>61.243139365425456</v>
       </c>
       <c r="D398" s="10">
-        <f>C398-_xlfn.FORECAST.ETS.CONFINT(A398,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>-31.933051251051445</v>
       </c>
       <c r="E398" s="10">
-        <f>C398+_xlfn.FORECAST.ETS.CONFINT(A398,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="2"/>
         <v>154.41932998190237</v>
       </c>
     </row>
@@ -13168,15 +13263,15 @@
         <v>45324</v>
       </c>
       <c r="C399">
-        <f>_xlfn.FORECAST.ETS(A399,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" ref="C399:C430" si="3">_xlfn.FORECAST.ETS(A399,$B$2:$B$366,$A$2:$A$366,1,1)</f>
         <v>66.716957191670204</v>
       </c>
       <c r="D399" s="10">
-        <f>C399-_xlfn.FORECAST.ETS.CONFINT(A399,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="D399:D430" si="4">C399-_xlfn.FORECAST.ETS.CONFINT(A399,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>-27.387538454538941</v>
       </c>
       <c r="E399" s="10">
-        <f>C399+_xlfn.FORECAST.ETS.CONFINT(A399,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="E399:E430" si="5">C399+_xlfn.FORECAST.ETS.CONFINT(A399,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>160.82145283787935</v>
       </c>
     </row>
@@ -13185,15 +13280,15 @@
         <v>45325</v>
       </c>
       <c r="C400">
-        <f>_xlfn.FORECAST.ETS(A400,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>32.714327772232373</v>
       </c>
       <c r="D400" s="10">
-        <f>C400-_xlfn.FORECAST.ETS.CONFINT(A400,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-62.315880698459019</v>
       </c>
       <c r="E400" s="10">
-        <f>C400+_xlfn.FORECAST.ETS.CONFINT(A400,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>127.74453624292377</v>
       </c>
     </row>
@@ -13202,15 +13297,15 @@
         <v>45326</v>
       </c>
       <c r="C401">
-        <f>_xlfn.FORECAST.ETS(A401,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>27.634045945072383</v>
       </c>
       <c r="D401" s="10">
-        <f>C401-_xlfn.FORECAST.ETS.CONFINT(A401,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-68.319380792982059</v>
       </c>
       <c r="E401" s="10">
-        <f>C401+_xlfn.FORECAST.ETS.CONFINT(A401,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>123.58747268312683</v>
       </c>
     </row>
@@ -13219,15 +13314,15 @@
         <v>45327</v>
       </c>
       <c r="C402">
-        <f>_xlfn.FORECAST.ETS(A402,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>42.124785278572844</v>
       </c>
       <c r="D402" s="10">
-        <f>C402-_xlfn.FORECAST.ETS.CONFINT(A402,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-57.025148418753744</v>
       </c>
       <c r="E402" s="10">
-        <f>C402+_xlfn.FORECAST.ETS.CONFINT(A402,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>141.27471897589942</v>
       </c>
     </row>
@@ -13236,15 +13331,15 @@
         <v>45328</v>
       </c>
       <c r="C403">
-        <f>_xlfn.FORECAST.ETS(A403,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>58.195527835600757</v>
       </c>
       <c r="D403" s="10">
-        <f>C403-_xlfn.FORECAST.ETS.CONFINT(A403,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-41.852022243247845</v>
       </c>
       <c r="E403" s="10">
-        <f>C403+_xlfn.FORECAST.ETS.CONFINT(A403,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>158.24307791444937</v>
       </c>
     </row>
@@ -13253,15 +13348,15 @@
         <v>45329</v>
       </c>
       <c r="C404">
-        <f>_xlfn.FORECAST.ETS(A404,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>77.059109824330548</v>
       </c>
       <c r="D404" s="10">
-        <f>C404-_xlfn.FORECAST.ETS.CONFINT(A404,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-23.884257394828822</v>
       </c>
       <c r="E404" s="10">
-        <f>C404+_xlfn.FORECAST.ETS.CONFINT(A404,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>178.00247704348993</v>
       </c>
     </row>
@@ -13270,15 +13365,15 @@
         <v>45330</v>
       </c>
       <c r="C405">
-        <f>_xlfn.FORECAST.ETS(A405,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>60.769948554439935</v>
       </c>
       <c r="D405" s="10">
-        <f>C405-_xlfn.FORECAST.ETS.CONFINT(A405,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-41.067505361010234</v>
       </c>
       <c r="E405" s="10">
-        <f>C405+_xlfn.FORECAST.ETS.CONFINT(A405,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>162.6074024698901</v>
       </c>
     </row>
@@ -13287,15 +13382,15 @@
         <v>45331</v>
       </c>
       <c r="C406">
-        <f>_xlfn.FORECAST.ETS(A406,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>66.243766380684676</v>
       </c>
       <c r="D406" s="10">
-        <f>C406-_xlfn.FORECAST.ETS.CONFINT(A406,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-36.486110099373434</v>
       </c>
       <c r="E406" s="10">
-        <f>C406+_xlfn.FORECAST.ETS.CONFINT(A406,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>168.97364286074279</v>
       </c>
     </row>
@@ -13304,15 +13399,15 @@
         <v>45332</v>
       </c>
       <c r="C407">
-        <f>_xlfn.FORECAST.ETS(A407,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>32.241136961246852</v>
       </c>
       <c r="D407" s="10">
-        <f>C407-_xlfn.FORECAST.ETS.CONFINT(A407,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-71.379561897291424</v>
       </c>
       <c r="E407" s="10">
-        <f>C407+_xlfn.FORECAST.ETS.CONFINT(A407,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>135.86183581978514</v>
       </c>
     </row>
@@ -13321,15 +13416,15 @@
         <v>45333</v>
       </c>
       <c r="C408">
-        <f>_xlfn.FORECAST.ETS(A408,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>27.160855134086862</v>
       </c>
       <c r="D408" s="10">
-        <f>C408-_xlfn.FORECAST.ETS.CONFINT(A408,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-77.349127606621821</v>
       </c>
       <c r="E408" s="10">
-        <f>C408+_xlfn.FORECAST.ETS.CONFINT(A408,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>131.67083787479555</v>
       </c>
     </row>
@@ -13338,15 +13433,15 @@
         <v>45334</v>
       </c>
       <c r="C409">
-        <f>_xlfn.FORECAST.ETS(A409,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>41.651594467587316</v>
       </c>
       <c r="D409" s="10">
-        <f>C409-_xlfn.FORECAST.ETS.CONFINT(A409,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-65.876920145688757</v>
       </c>
       <c r="E409" s="10">
-        <f>C409+_xlfn.FORECAST.ETS.CONFINT(A409,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>149.18010908086339</v>
       </c>
     </row>
@@ -13355,15 +13450,15 @@
         <v>45335</v>
       </c>
       <c r="C410">
-        <f>_xlfn.FORECAST.ETS(A410,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>57.722337024615243</v>
       </c>
       <c r="D410" s="10">
-        <f>C410-_xlfn.FORECAST.ETS.CONFINT(A410,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-50.675139147176949</v>
       </c>
       <c r="E410" s="10">
-        <f>C410+_xlfn.FORECAST.ETS.CONFINT(A410,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>166.11981319640745</v>
       </c>
     </row>
@@ -13372,15 +13467,15 @@
         <v>45336</v>
       </c>
       <c r="C411">
-        <f>_xlfn.FORECAST.ETS(A411,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>76.585919013345034</v>
       </c>
       <c r="D411" s="10">
-        <f>C411-_xlfn.FORECAST.ETS.CONFINT(A411,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-32.679458854618687</v>
       </c>
       <c r="E411" s="10">
-        <f>C411+_xlfn.FORECAST.ETS.CONFINT(A411,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>185.85129688130877</v>
       </c>
     </row>
@@ -13389,15 +13484,15 @@
         <v>45337</v>
       </c>
       <c r="C412">
-        <f>_xlfn.FORECAST.ETS(A412,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>60.296757743454414</v>
       </c>
       <c r="D412" s="10">
-        <f>C412-_xlfn.FORECAST.ETS.CONFINT(A412,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-49.835506725644684</v>
       </c>
       <c r="E412" s="10">
-        <f>C412+_xlfn.FORECAST.ETS.CONFINT(A412,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>170.42902221255352</v>
       </c>
     </row>
@@ -13406,15 +13501,15 @@
         <v>45338</v>
       </c>
       <c r="C413">
-        <f>_xlfn.FORECAST.ETS(A413,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>65.770575569699162</v>
       </c>
       <c r="D413" s="10">
-        <f>C413-_xlfn.FORECAST.ETS.CONFINT(A413,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-45.227603745605293</v>
       </c>
       <c r="E413" s="10">
-        <f>C413+_xlfn.FORECAST.ETS.CONFINT(A413,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>176.7687548850036</v>
       </c>
     </row>
@@ -13423,15 +13518,15 @@
         <v>45339</v>
       </c>
       <c r="C414">
-        <f>_xlfn.FORECAST.ETS(A414,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>31.767946150261324</v>
       </c>
       <c r="D414" s="10">
-        <f>C414-_xlfn.FORECAST.ETS.CONFINT(A414,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-80.095218228374577</v>
       </c>
       <c r="E414" s="10">
-        <f>C414+_xlfn.FORECAST.ETS.CONFINT(A414,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>143.63111052889724</v>
       </c>
     </row>
@@ -13440,15 +13535,15 @@
         <v>45340</v>
       </c>
       <c r="C415">
-        <f>_xlfn.FORECAST.ETS(A415,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>26.687664323101341</v>
       </c>
       <c r="D415" s="10">
-        <f>C415-_xlfn.FORECAST.ETS.CONFINT(A415,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-86.039595996084287</v>
       </c>
       <c r="E415" s="10">
-        <f>C415+_xlfn.FORECAST.ETS.CONFINT(A415,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>139.41492464228696</v>
       </c>
     </row>
@@ -13457,15 +13552,15 @@
         <v>45341</v>
       </c>
       <c r="C416">
-        <f>_xlfn.FORECAST.ETS(A416,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>41.178403656601802</v>
       </c>
       <c r="D416" s="10">
-        <f>C416-_xlfn.FORECAST.ETS.CONFINT(A416,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-74.424747808252761</v>
       </c>
       <c r="E416" s="10">
-        <f>C416+_xlfn.FORECAST.ETS.CONFINT(A416,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>156.78155512145636</v>
       </c>
     </row>
@@ -13474,15 +13569,15 @@
         <v>45342</v>
       </c>
       <c r="C417">
-        <f>_xlfn.FORECAST.ETS(A417,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>57.249146213629714</v>
       </c>
       <c r="D417" s="10">
-        <f>C417-_xlfn.FORECAST.ETS.CONFINT(A417,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-59.20153523118303</v>
       </c>
       <c r="E417" s="10">
-        <f>C417+_xlfn.FORECAST.ETS.CONFINT(A417,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>173.69982765844247</v>
       </c>
     </row>
@@ -13491,15 +13586,15 @@
         <v>45343</v>
       </c>
       <c r="C418">
-        <f>_xlfn.FORECAST.ETS(A418,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>76.112728202359506</v>
       </c>
       <c r="D418" s="10">
-        <f>C418-_xlfn.FORECAST.ETS.CONFINT(A418,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-41.184939100214436</v>
       </c>
       <c r="E418" s="10">
-        <f>C418+_xlfn.FORECAST.ETS.CONFINT(A418,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>193.41039550493343</v>
       </c>
     </row>
@@ -13508,15 +13603,15 @@
         <v>45344</v>
       </c>
       <c r="C419">
-        <f>_xlfn.FORECAST.ETS(A419,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>59.823566932468886</v>
       </c>
       <c r="D419" s="10">
-        <f>C419-_xlfn.FORECAST.ETS.CONFINT(A419,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-58.320572182040173</v>
       </c>
       <c r="E419" s="10">
-        <f>C419+_xlfn.FORECAST.ETS.CONFINT(A419,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>177.96770604697795</v>
       </c>
     </row>
@@ -13525,15 +13620,15 @@
         <v>45345</v>
       </c>
       <c r="C420">
-        <f>_xlfn.FORECAST.ETS(A420,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>65.297384758713633</v>
       </c>
       <c r="D420" s="10">
-        <f>C420-_xlfn.FORECAST.ETS.CONFINT(A420,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-53.692741335516715</v>
       </c>
       <c r="E420" s="10">
-        <f>C420+_xlfn.FORECAST.ETS.CONFINT(A420,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>184.28751085294397</v>
       </c>
     </row>
@@ -13542,15 +13637,15 @@
         <v>45346</v>
       </c>
       <c r="C421">
-        <f>_xlfn.FORECAST.ETS(A421,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>31.294755339275802</v>
       </c>
       <c r="D421" s="10">
-        <f>C421-_xlfn.FORECAST.ETS.CONFINT(A421,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-88.540901285005134</v>
       </c>
       <c r="E421" s="10">
-        <f>C421+_xlfn.FORECAST.ETS.CONFINT(A421,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>151.13041196355675</v>
       </c>
     </row>
@@ -13559,15 +13654,15 @@
         <v>45347</v>
       </c>
       <c r="C422">
-        <f>_xlfn.FORECAST.ETS(A422,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>26.214473512115813</v>
       </c>
       <c r="D422" s="10">
-        <f>C422-_xlfn.FORECAST.ETS.CONFINT(A422,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-94.466284774256451</v>
       </c>
       <c r="E422" s="10">
-        <f>C422+_xlfn.FORECAST.ETS.CONFINT(A422,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>146.89523179848808</v>
       </c>
     </row>
@@ -13576,15 +13671,15 @@
         <v>45348</v>
       </c>
       <c r="C423">
-        <f>_xlfn.FORECAST.ETS(A423,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>40.705212845616273</v>
       </c>
       <c r="D423" s="10">
-        <f>C423-_xlfn.FORECAST.ETS.CONFINT(A423,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-82.734327056191418</v>
       </c>
       <c r="E423" s="10">
-        <f>C423+_xlfn.FORECAST.ETS.CONFINT(A423,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>164.14475274742398</v>
       </c>
     </row>
@@ -13593,15 +13688,15 @@
         <v>45349</v>
       </c>
       <c r="C424">
-        <f>_xlfn.FORECAST.ETS(A424,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>56.775955402644186</v>
       </c>
       <c r="D424" s="10">
-        <f>C424-_xlfn.FORECAST.ETS.CONFINT(A424,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-67.494904095472549</v>
       </c>
       <c r="E424" s="10">
-        <f>C424+_xlfn.FORECAST.ETS.CONFINT(A424,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>181.04681490076092</v>
       </c>
     </row>
@@ -13610,15 +13705,15 @@
         <v>45350</v>
       </c>
       <c r="C425">
-        <f>_xlfn.FORECAST.ETS(A425,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>75.639537391373977</v>
       </c>
       <c r="D425" s="10">
-        <f>C425-_xlfn.FORECAST.ETS.CONFINT(A425,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-49.462470528208655</v>
       </c>
       <c r="E425" s="10">
-        <f>C425+_xlfn.FORECAST.ETS.CONFINT(A425,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>200.74154531095661</v>
       </c>
     </row>
@@ -13627,15 +13722,15 @@
         <v>45351</v>
       </c>
       <c r="C426">
-        <f>_xlfn.FORECAST.ETS(A426,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>59.350376121483364</v>
       </c>
       <c r="D426" s="10">
-        <f>C426-_xlfn.FORECAST.ETS.CONFINT(A426,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-66.582629671327183</v>
       </c>
       <c r="E426" s="10">
-        <f>C426+_xlfn.FORECAST.ETS.CONFINT(A426,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>185.2833819142939</v>
       </c>
     </row>
@@ -13644,15 +13739,15 @@
         <v>45352</v>
       </c>
       <c r="C427">
-        <f>_xlfn.FORECAST.ETS(A427,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>64.824193947728105</v>
       </c>
       <c r="D427" s="10">
-        <f>C427-_xlfn.FORECAST.ETS.CONFINT(A427,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-61.939679255219701</v>
       </c>
       <c r="E427" s="10">
-        <f>C427+_xlfn.FORECAST.ETS.CONFINT(A427,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>191.5880671506759</v>
       </c>
     </row>
@@ -13661,15 +13756,15 @@
         <v>45353</v>
       </c>
       <c r="C428">
-        <f>_xlfn.FORECAST.ETS(A428,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>30.821564528290281</v>
       </c>
       <c r="D428" s="10">
-        <f>C428-_xlfn.FORECAST.ETS.CONFINT(A428,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-96.773065183247311</v>
       </c>
       <c r="E428" s="10">
-        <f>C428+_xlfn.FORECAST.ETS.CONFINT(A428,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>158.41619423982786</v>
       </c>
     </row>
@@ -13678,15 +13773,15 @@
         <v>45354</v>
       </c>
       <c r="C429">
-        <f>_xlfn.FORECAST.ETS(A429,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>25.741282701130292</v>
       </c>
       <c r="D429" s="10">
-        <f>C429-_xlfn.FORECAST.ETS.CONFINT(A429,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-102.68401167251049</v>
       </c>
       <c r="E429" s="10">
-        <f>C429+_xlfn.FORECAST.ETS.CONFINT(A429,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>154.16657707477108</v>
       </c>
     </row>
@@ -13695,15 +13790,15 @@
         <v>45355</v>
       </c>
       <c r="C430">
-        <f>_xlfn.FORECAST.ETS(A430,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="3"/>
         <v>40.232022034630745</v>
       </c>
       <c r="D430" s="10">
-        <f>C430-_xlfn.FORECAST.ETS.CONFINT(A430,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="4"/>
         <v>-90.854074637018982</v>
       </c>
       <c r="E430" s="10">
-        <f>C430+_xlfn.FORECAST.ETS.CONFINT(A430,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="5"/>
         <v>171.31811870628047</v>
       </c>
     </row>
@@ -13712,15 +13807,15 @@
         <v>45356</v>
       </c>
       <c r="C431">
-        <f>_xlfn.FORECAST.ETS(A431,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" ref="C431:C462" si="6">_xlfn.FORECAST.ETS(A431,$B$2:$B$366,$A$2:$A$366,1,1)</f>
         <v>56.302764591658672</v>
       </c>
       <c r="D431" s="10">
-        <f>C431-_xlfn.FORECAST.ETS.CONFINT(A431,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="D431:D462" si="7">C431-_xlfn.FORECAST.ETS.CONFINT(A431,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>-75.602344910257472</v>
       </c>
       <c r="E431" s="10">
-        <f>C431+_xlfn.FORECAST.ETS.CONFINT(A431,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="E431:E462" si="8">C431+_xlfn.FORECAST.ETS.CONFINT(A431,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>188.20787409357482</v>
       </c>
     </row>
@@ -13729,15 +13824,15 @@
         <v>45357</v>
       </c>
       <c r="C432">
-        <f>_xlfn.FORECAST.ETS(A432,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>75.166346580388463</v>
       </c>
       <c r="D432" s="10">
-        <f>C432-_xlfn.FORECAST.ETS.CONFINT(A432,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-57.557881920917382</v>
       </c>
       <c r="E432" s="10">
-        <f>C432+_xlfn.FORECAST.ETS.CONFINT(A432,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>207.89057508169429</v>
       </c>
     </row>
@@ -13746,15 +13841,15 @@
         <v>45358</v>
       </c>
       <c r="C433">
-        <f>_xlfn.FORECAST.ETS(A433,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>58.877185310497843</v>
       </c>
       <c r="D433" s="10">
-        <f>C433-_xlfn.FORECAST.ETS.CONFINT(A433,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-74.66628266072982</v>
       </c>
       <c r="E433" s="10">
-        <f>C433+_xlfn.FORECAST.ETS.CONFINT(A433,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>192.42065328172552</v>
       </c>
     </row>
@@ -13763,15 +13858,15 @@
         <v>45359</v>
       </c>
       <c r="C434">
-        <f>_xlfn.FORECAST.ETS(A434,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>64.351003136742577</v>
       </c>
       <c r="D434" s="10">
-        <f>C434-_xlfn.FORECAST.ETS.CONFINT(A434,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-70.011838727252865</v>
       </c>
       <c r="E434" s="10">
-        <f>C434+_xlfn.FORECAST.ETS.CONFINT(A434,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>198.71384500073802</v>
       </c>
     </row>
@@ -13780,15 +13875,15 @@
         <v>45360</v>
       </c>
       <c r="C435">
-        <f>_xlfn.FORECAST.ETS(A435,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>30.348373717304753</v>
       </c>
       <c r="D435" s="10">
-        <f>C435-_xlfn.FORECAST.ETS.CONFINT(A435,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-104.83399007596964</v>
       </c>
       <c r="E435" s="10">
-        <f>C435+_xlfn.FORECAST.ETS.CONFINT(A435,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>165.53073751057914</v>
       </c>
     </row>
@@ -13797,15 +13892,15 @@
         <v>45361</v>
       </c>
       <c r="C436">
-        <f>_xlfn.FORECAST.ETS(A436,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>25.26809189014477</v>
       </c>
       <c r="D436" s="10">
-        <f>C436-_xlfn.FORECAST.ETS.CONFINT(A436,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-110.73395515399667</v>
       </c>
       <c r="E436" s="10">
-        <f>C436+_xlfn.FORECAST.ETS.CONFINT(A436,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>161.27013893428622</v>
       </c>
     </row>
@@ -13814,15 +13909,15 @@
         <v>45362</v>
       </c>
       <c r="C437">
-        <f>_xlfn.FORECAST.ETS(A437,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>39.758831223645231</v>
       </c>
       <c r="D437" s="10">
-        <f>C437-_xlfn.FORECAST.ETS.CONFINT(A437,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-98.820791935401687</v>
       </c>
       <c r="E437" s="10">
-        <f>C437+_xlfn.FORECAST.ETS.CONFINT(A437,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>178.33845438269213</v>
       </c>
     </row>
@@ -13831,15 +13926,15 @@
         <v>45363</v>
       </c>
       <c r="C438">
-        <f>_xlfn.FORECAST.ETS(A438,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>55.829573780673144</v>
       </c>
       <c r="D438" s="10">
-        <f>C438-_xlfn.FORECAST.ETS.CONFINT(A438,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-83.559753371288792</v>
       </c>
       <c r="E438" s="10">
-        <f>C438+_xlfn.FORECAST.ETS.CONFINT(A438,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>195.21890093263508</v>
       </c>
     </row>
@@ -13848,15 +13943,15 @@
         <v>45364</v>
       </c>
       <c r="C439">
-        <f>_xlfn.FORECAST.ETS(A439,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>74.693155769402935</v>
       </c>
       <c r="D439" s="10">
-        <f>C439-_xlfn.FORECAST.ETS.CONFINT(A439,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-65.506192409794679</v>
       </c>
       <c r="E439" s="10">
-        <f>C439+_xlfn.FORECAST.ETS.CONFINT(A439,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>214.89250394860056</v>
       </c>
     </row>
@@ -13865,15 +13960,15 @@
         <v>45365</v>
       </c>
       <c r="C440">
-        <f>_xlfn.FORECAST.ETS(A440,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>58.403994499512315</v>
       </c>
       <c r="D440" s="10">
-        <f>C440-_xlfn.FORECAST.ETS.CONFINT(A440,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-82.605701672060292</v>
       </c>
       <c r="E440" s="10">
-        <f>C440+_xlfn.FORECAST.ETS.CONFINT(A440,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>199.41369067108494</v>
       </c>
     </row>
@@ -13882,15 +13977,15 @@
         <v>45366</v>
       </c>
       <c r="C441">
-        <f>_xlfn.FORECAST.ETS(A441,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>63.877812325757063</v>
       </c>
       <c r="D441" s="10">
-        <f>C441-_xlfn.FORECAST.ETS.CONFINT(A441,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-77.942568504957265</v>
       </c>
       <c r="E441" s="10">
-        <f>C441+_xlfn.FORECAST.ETS.CONFINT(A441,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>205.6981931564714</v>
       </c>
     </row>
@@ -13899,15 +13994,15 @@
         <v>45367</v>
       </c>
       <c r="C442">
-        <f>_xlfn.FORECAST.ETS(A442,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>29.875182906319232</v>
       </c>
       <c r="D442" s="10">
-        <f>C442-_xlfn.FORECAST.ETS.CONFINT(A442,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-112.75622872902457</v>
       </c>
       <c r="E442" s="10">
-        <f>C442+_xlfn.FORECAST.ETS.CONFINT(A442,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>172.50659454166302</v>
       </c>
     </row>
@@ -13916,15 +14011,15 @@
         <v>45368</v>
       </c>
       <c r="C443">
-        <f>_xlfn.FORECAST.ETS(A443,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>24.794901079159242</v>
       </c>
       <c r="D443" s="10">
-        <f>C443-_xlfn.FORECAST.ETS.CONFINT(A443,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-118.64789676819001</v>
       </c>
       <c r="E443" s="10">
-        <f>C443+_xlfn.FORECAST.ETS.CONFINT(A443,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>168.2376989265085</v>
       </c>
     </row>
@@ -13933,15 +14028,15 @@
         <v>45369</v>
       </c>
       <c r="C444">
-        <f>_xlfn.FORECAST.ETS(A444,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>39.285640412659703</v>
       </c>
       <c r="D444" s="10">
-        <f>C444-_xlfn.FORECAST.ETS.CONFINT(A444,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-106.66315469039351</v>
       </c>
       <c r="E444" s="10">
-        <f>C444+_xlfn.FORECAST.ETS.CONFINT(A444,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>185.2344355157129</v>
       </c>
     </row>
@@ -13950,15 +14045,15 @@
         <v>45370</v>
       </c>
       <c r="C445">
-        <f>_xlfn.FORECAST.ETS(A445,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>55.356382969687616</v>
       </c>
       <c r="D445" s="10">
-        <f>C445-_xlfn.FORECAST.ETS.CONFINT(A445,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-91.395160435733516</v>
       </c>
       <c r="E445" s="10">
-        <f>C445+_xlfn.FORECAST.ETS.CONFINT(A445,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>202.10792637510875</v>
       </c>
     </row>
@@ -13967,15 +14062,15 @@
         <v>45371</v>
       </c>
       <c r="C446">
-        <f>_xlfn.FORECAST.ETS(A446,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>74.219964958417407</v>
       </c>
       <c r="D446" s="10">
-        <f>C446-_xlfn.FORECAST.ETS.CONFINT(A446,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-73.334806971555807</v>
       </c>
       <c r="E446" s="10">
-        <f>C446+_xlfn.FORECAST.ETS.CONFINT(A446,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>221.77473688839063</v>
       </c>
     </row>
@@ -13984,15 +14079,15 @@
         <v>45372</v>
       </c>
       <c r="C447">
-        <f>_xlfn.FORECAST.ETS(A447,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>57.930803688526794</v>
       </c>
       <c r="D447" s="10">
-        <f>C447-_xlfn.FORECAST.ETS.CONFINT(A447,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-90.42768382008444</v>
       </c>
       <c r="E447" s="10">
-        <f>C447+_xlfn.FORECAST.ETS.CONFINT(A447,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>206.28929119713803</v>
       </c>
     </row>
@@ -14001,15 +14096,15 @@
         <v>45373</v>
       </c>
       <c r="C448">
-        <f>_xlfn.FORECAST.ETS(A448,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>63.404621514771534</v>
       </c>
       <c r="D448" s="10">
-        <f>C448-_xlfn.FORECAST.ETS.CONFINT(A448,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-85.758075306492756</v>
       </c>
       <c r="E448" s="10">
-        <f>C448+_xlfn.FORECAST.ETS.CONFINT(A448,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>212.56731833603584</v>
       </c>
     </row>
@@ -14018,15 +14113,15 @@
         <v>45374</v>
       </c>
       <c r="C449">
-        <f>_xlfn.FORECAST.ETS(A449,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>29.401992095333711</v>
       </c>
       <c r="D449" s="10">
-        <f>C449-_xlfn.FORECAST.ETS.CONFINT(A449,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-120.56541430440872</v>
       </c>
       <c r="E449" s="10">
-        <f>C449+_xlfn.FORECAST.ETS.CONFINT(A449,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>179.36939849507615</v>
       </c>
     </row>
@@ -14035,15 +14130,15 @@
         <v>45375</v>
       </c>
       <c r="C450">
-        <f>_xlfn.FORECAST.ETS(A450,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>24.321710268173721</v>
       </c>
       <c r="D450" s="10">
-        <f>C450-_xlfn.FORECAST.ETS.CONFINT(A450,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-126.45091236329802</v>
       </c>
       <c r="E450" s="10">
-        <f>C450+_xlfn.FORECAST.ETS.CONFINT(A450,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>175.09433289964545</v>
       </c>
     </row>
@@ -14052,15 +14147,15 @@
         <v>45376</v>
       </c>
       <c r="C451">
-        <f>_xlfn.FORECAST.ETS(A451,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>38.812449601674174</v>
       </c>
       <c r="D451" s="10">
-        <f>C451-_xlfn.FORECAST.ETS.CONFINT(A451,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-114.40396724057466</v>
       </c>
       <c r="E451" s="10">
-        <f>C451+_xlfn.FORECAST.ETS.CONFINT(A451,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>192.02886644392299</v>
       </c>
     </row>
@@ -14069,15 +14164,15 @@
         <v>45377</v>
       </c>
       <c r="C452">
-        <f>_xlfn.FORECAST.ETS(A452,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>54.883192158702101</v>
       </c>
       <c r="D452" s="10">
-        <f>C452-_xlfn.FORECAST.ETS.CONFINT(A452,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-99.130897958670161</v>
       </c>
       <c r="E452" s="10">
-        <f>C452+_xlfn.FORECAST.ETS.CONFINT(A452,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>208.89728227607435</v>
       </c>
     </row>
@@ -14086,15 +14181,15 @@
         <v>45378</v>
       </c>
       <c r="C453">
-        <f>_xlfn.FORECAST.ETS(A453,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>73.746774147431893</v>
       </c>
       <c r="D453" s="10">
-        <f>C453-_xlfn.FORECAST.ETS.CONFINT(A453,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-81.065597572500053</v>
       </c>
       <c r="E453" s="10">
-        <f>C453+_xlfn.FORECAST.ETS.CONFINT(A453,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>228.55914586736384</v>
       </c>
     </row>
@@ -14103,15 +14198,15 @@
         <v>45379</v>
       </c>
       <c r="C454">
-        <f>_xlfn.FORECAST.ETS(A454,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>57.457612877541273</v>
       </c>
       <c r="D454" s="10">
-        <f>C454-_xlfn.FORECAST.ETS.CONFINT(A454,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-98.15365336013474</v>
       </c>
       <c r="E454" s="10">
-        <f>C454+_xlfn.FORECAST.ETS.CONFINT(A454,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>213.06887911521727</v>
       </c>
     </row>
@@ -14120,15 +14215,15 @@
         <v>45380</v>
       </c>
       <c r="C455">
-        <f>_xlfn.FORECAST.ETS(A455,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>62.931430703786013</v>
       </c>
       <c r="D455" s="10">
-        <f>C455-_xlfn.FORECAST.ETS.CONFINT(A455,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-93.479347453666122</v>
       </c>
       <c r="E455" s="10">
-        <f>C455+_xlfn.FORECAST.ETS.CONFINT(A455,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>219.34220886123816</v>
       </c>
     </row>
@@ -14137,15 +14232,15 @@
         <v>45381</v>
       </c>
       <c r="C456">
-        <f>_xlfn.FORECAST.ETS(A456,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>28.928801284348182</v>
       </c>
       <c r="D456" s="10">
-        <f>C456-_xlfn.FORECAST.ETS.CONFINT(A456,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-128.28211058324763</v>
       </c>
       <c r="E456" s="10">
-        <f>C456+_xlfn.FORECAST.ETS.CONFINT(A456,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>186.13971315194402</v>
       </c>
     </row>
@@ -14154,15 +14249,15 @@
         <v>45382</v>
       </c>
       <c r="C457">
-        <f>_xlfn.FORECAST.ETS(A457,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>23.8485194571882</v>
       </c>
       <c r="D457" s="10">
-        <f>C457-_xlfn.FORECAST.ETS.CONFINT(A457,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-134.16315220306254</v>
       </c>
       <c r="E457" s="10">
-        <f>C457+_xlfn.FORECAST.ETS.CONFINT(A457,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>181.86019111743892</v>
       </c>
     </row>
@@ -14171,15 +14266,15 @@
         <v>45383</v>
       </c>
       <c r="C458">
-        <f>_xlfn.FORECAST.ETS(A458,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>38.33925879068866</v>
       </c>
       <c r="D458" s="10">
-        <f>C458-_xlfn.FORECAST.ETS.CONFINT(A458,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-122.06167601555757</v>
       </c>
       <c r="E458" s="10">
-        <f>C458+_xlfn.FORECAST.ETS.CONFINT(A458,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>198.74019359693489</v>
       </c>
     </row>
@@ -14188,15 +14283,15 @@
         <v>45384</v>
       </c>
       <c r="C459">
-        <f>_xlfn.FORECAST.ETS(A459,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>54.410001347716573</v>
       </c>
       <c r="D459" s="10">
-        <f>C459-_xlfn.FORECAST.ETS.CONFINT(A459,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-106.78505766552736</v>
       </c>
       <c r="E459" s="10">
-        <f>C459+_xlfn.FORECAST.ETS.CONFINT(A459,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>215.60506036096052</v>
       </c>
     </row>
@@ -14205,15 +14300,15 @@
         <v>45385</v>
       </c>
       <c r="C460">
-        <f>_xlfn.FORECAST.ETS(A460,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>73.273583336446364</v>
       </c>
       <c r="D460" s="10">
-        <f>C460-_xlfn.FORECAST.ETS.CONFINT(A460,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-88.716309936510015</v>
       </c>
       <c r="E460" s="10">
-        <f>C460+_xlfn.FORECAST.ETS.CONFINT(A460,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>235.26347660940274</v>
       </c>
     </row>
@@ -14222,15 +14317,15 @@
         <v>45386</v>
       </c>
       <c r="C461">
-        <f>_xlfn.FORECAST.ETS(A461,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>56.984422066555744</v>
       </c>
       <c r="D461" s="10">
-        <f>C461-_xlfn.FORECAST.ETS.CONFINT(A461,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-105.80101845295016</v>
       </c>
       <c r="E461" s="10">
-        <f>C461+_xlfn.FORECAST.ETS.CONFINT(A461,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>219.76986258606163</v>
       </c>
     </row>
@@ -14239,15 +14334,15 @@
         <v>45387</v>
       </c>
       <c r="C462">
-        <f>_xlfn.FORECAST.ETS(A462,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="6"/>
         <v>62.458239892800485</v>
       </c>
       <c r="D462" s="10">
-        <f>C462-_xlfn.FORECAST.ETS.CONFINT(A462,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="7"/>
         <v>-101.12346372783892</v>
       </c>
       <c r="E462" s="10">
-        <f>C462+_xlfn.FORECAST.ETS.CONFINT(A462,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="8"/>
         <v>226.03994351343991</v>
       </c>
     </row>
@@ -14256,15 +14351,15 @@
         <v>45388</v>
       </c>
       <c r="C463">
-        <f>_xlfn.FORECAST.ETS(A463,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" ref="C463:C494" si="9">_xlfn.FORECAST.ETS(A463,$B$2:$B$366,$A$2:$A$366,1,1)</f>
         <v>28.455610473362661</v>
       </c>
       <c r="D463" s="10">
-        <f>C463-_xlfn.FORECAST.ETS.CONFINT(A463,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="D463:D494" si="10">C463-_xlfn.FORECAST.ETS.CONFINT(A463,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>-135.92307490584739</v>
       </c>
       <c r="E463" s="10">
-        <f>C463+_xlfn.FORECAST.ETS.CONFINT(A463,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="E463:E494" si="11">C463+_xlfn.FORECAST.ETS.CONFINT(A463,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>192.83429585257272</v>
       </c>
     </row>
@@ -14273,15 +14368,15 @@
         <v>45389</v>
       </c>
       <c r="C464">
-        <f>_xlfn.FORECAST.ETS(A464,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>23.375328646202671</v>
       </c>
       <c r="D464" s="10">
-        <f>C464-_xlfn.FORECAST.ETS.CONFINT(A464,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-141.80105988841683</v>
       </c>
       <c r="E464" s="10">
-        <f>C464+_xlfn.FORECAST.ETS.CONFINT(A464,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>188.55171718082215</v>
       </c>
     </row>
@@ -14290,15 +14385,15 @@
         <v>45390</v>
       </c>
       <c r="C465">
-        <f>_xlfn.FORECAST.ETS(A465,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>37.866067979703132</v>
       </c>
       <c r="D465" s="10">
-        <f>C465-_xlfn.FORECAST.ETS.CONFINT(A465,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-129.65141892907505</v>
       </c>
       <c r="E465" s="10">
-        <f>C465+_xlfn.FORECAST.ETS.CONFINT(A465,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>205.38355488848131</v>
       </c>
     </row>
@@ -14307,15 +14402,15 @@
         <v>45391</v>
       </c>
       <c r="C466">
-        <f>_xlfn.FORECAST.ETS(A466,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>53.936810536731045</v>
       </c>
       <c r="D466" s="10">
-        <f>C466-_xlfn.FORECAST.ETS.CONFINT(A466,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-114.37250565419352</v>
       </c>
       <c r="E466" s="10">
-        <f>C466+_xlfn.FORECAST.ETS.CONFINT(A466,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>222.24612672765562</v>
       </c>
     </row>
@@ -14324,15 +14419,15 @@
         <v>45392</v>
       </c>
       <c r="C467">
-        <f>_xlfn.FORECAST.ETS(A467,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>72.800392525460836</v>
       </c>
       <c r="D467" s="10">
-        <f>C467-_xlfn.FORECAST.ETS.CONFINT(A467,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-96.301544519584922</v>
       </c>
       <c r="E467" s="10">
-        <f>C467+_xlfn.FORECAST.ETS.CONFINT(A467,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>241.90232957050659</v>
       </c>
     </row>
@@ -14341,15 +14436,15 @@
         <v>45393</v>
       </c>
       <c r="C468">
-        <f>_xlfn.FORECAST.ETS(A468,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>56.511231255570223</v>
       </c>
       <c r="D468" s="10">
-        <f>C468-_xlfn.FORECAST.ETS.CONFINT(A468,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-113.38411991370937</v>
       </c>
       <c r="E468" s="10">
-        <f>C468+_xlfn.FORECAST.ETS.CONFINT(A468,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>226.40658242484983</v>
       </c>
     </row>
@@ -14358,15 +14453,15 @@
         <v>45394</v>
       </c>
       <c r="C469">
-        <f>_xlfn.FORECAST.ETS(A469,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>61.985049081814964</v>
       </c>
       <c r="D469" s="10">
-        <f>C469-_xlfn.FORECAST.ETS.CONFINT(A469,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-108.70451113733088</v>
       </c>
       <c r="E469" s="10">
-        <f>C469+_xlfn.FORECAST.ETS.CONFINT(A469,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>232.67460930096081</v>
       </c>
     </row>
@@ -14375,15 +14470,15 @@
         <v>45395</v>
       </c>
       <c r="C470">
-        <f>_xlfn.FORECAST.ETS(A470,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>27.98241966237714</v>
       </c>
       <c r="D470" s="10">
-        <f>C470-_xlfn.FORECAST.ETS.CONFINT(A470,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-143.5021461460783</v>
       </c>
       <c r="E470" s="10">
-        <f>C470+_xlfn.FORECAST.ETS.CONFINT(A470,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>199.46698547083258</v>
       </c>
     </row>
@@ -14392,15 +14487,15 @@
         <v>45396</v>
       </c>
       <c r="C471">
-        <f>_xlfn.FORECAST.ETS(A471,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>22.90213783521715</v>
       </c>
       <c r="D471" s="10">
-        <f>C471-_xlfn.FORECAST.ETS.CONFINT(A471,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-149.37823167498041</v>
       </c>
       <c r="E471" s="10">
-        <f>C471+_xlfn.FORECAST.ETS.CONFINT(A471,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>195.18250734541473</v>
       </c>
     </row>
@@ -14409,15 +14504,15 @@
         <v>45397</v>
       </c>
       <c r="C472">
-        <f>_xlfn.FORECAST.ETS(A472,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>37.392877168717604</v>
       </c>
       <c r="D472" s="10">
-        <f>C472-_xlfn.FORECAST.ETS.CONFINT(A472,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-137.18577309672239</v>
       </c>
       <c r="E472" s="10">
-        <f>C472+_xlfn.FORECAST.ETS.CONFINT(A472,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>211.97152743415759</v>
       </c>
     </row>
@@ -14426,15 +14521,15 @@
         <v>45398</v>
       </c>
       <c r="C473">
-        <f>_xlfn.FORECAST.ETS(A473,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>53.463619725745531</v>
       </c>
       <c r="D473" s="10">
-        <f>C473-_xlfn.FORECAST.ETS.CONFINT(A473,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-121.90560702679014</v>
       </c>
       <c r="E473" s="10">
-        <f>C473+_xlfn.FORECAST.ETS.CONFINT(A473,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>228.8328464782812</v>
       </c>
     </row>
@@ -14443,15 +14538,15 @@
         <v>45399</v>
       </c>
       <c r="C474">
-        <f>_xlfn.FORECAST.ETS(A474,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>72.327201714475322</v>
       </c>
       <c r="D474" s="10">
-        <f>C474-_xlfn.FORECAST.ETS.CONFINT(A474,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-103.83345889094709</v>
       </c>
       <c r="E474" s="10">
-        <f>C474+_xlfn.FORECAST.ETS.CONFINT(A474,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>248.48786231989772</v>
       </c>
     </row>
@@ -14460,15 +14555,15 @@
         <v>45400</v>
       </c>
       <c r="C475">
-        <f>_xlfn.FORECAST.ETS(A475,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>56.038040444584702</v>
       </c>
       <c r="D475" s="10">
-        <f>C475-_xlfn.FORECAST.ETS.CONFINT(A475,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-120.91491214305259</v>
       </c>
       <c r="E475" s="10">
-        <f>C475+_xlfn.FORECAST.ETS.CONFINT(A475,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>232.99099303222201</v>
       </c>
     </row>
@@ -14477,15 +14572,15 @@
         <v>45401</v>
       </c>
       <c r="C476">
-        <f>_xlfn.FORECAST.ETS(A476,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>61.511858270829443</v>
       </c>
       <c r="D476" s="10">
-        <f>C476-_xlfn.FORECAST.ETS.CONFINT(A476,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-116.23424516585291</v>
       </c>
       <c r="E476" s="10">
-        <f>C476+_xlfn.FORECAST.ETS.CONFINT(A476,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>239.25796170751178</v>
       </c>
     </row>
@@ -14494,15 +14589,15 @@
         <v>45402</v>
       </c>
       <c r="C477">
-        <f>_xlfn.FORECAST.ETS(A477,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>27.509228851391612</v>
       </c>
       <c r="D477" s="10">
-        <f>C477-_xlfn.FORECAST.ETS.CONFINT(A477,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-151.03088501317512</v>
       </c>
       <c r="E477" s="10">
-        <f>C477+_xlfn.FORECAST.ETS.CONFINT(A477,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>206.04934271595835</v>
       </c>
     </row>
@@ -14511,15 +14606,15 @@
         <v>45403</v>
       </c>
       <c r="C478">
-        <f>_xlfn.FORECAST.ETS(A478,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>22.428947024231629</v>
       </c>
       <c r="D478" s="10">
-        <f>C478-_xlfn.FORECAST.ETS.CONFINT(A478,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-156.90603753410494</v>
       </c>
       <c r="E478" s="10">
-        <f>C478+_xlfn.FORECAST.ETS.CONFINT(A478,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>201.7639315825682</v>
       </c>
     </row>
@@ -14528,15 +14623,15 @@
         <v>45404</v>
       </c>
       <c r="C479">
-        <f>_xlfn.FORECAST.ETS(A479,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>36.91968635773209</v>
       </c>
       <c r="D479" s="10">
-        <f>C479-_xlfn.FORECAST.ETS.CONFINT(A479,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-144.67530021818641</v>
       </c>
       <c r="E479" s="10">
-        <f>C479+_xlfn.FORECAST.ETS.CONFINT(A479,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>218.51467293365056</v>
       </c>
     </row>
@@ -14545,15 +14640,15 @@
         <v>45405</v>
       </c>
       <c r="C480">
-        <f>_xlfn.FORECAST.ETS(A480,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>52.990428914760002</v>
       </c>
       <c r="D480" s="10">
-        <f>C480-_xlfn.FORECAST.ETS.CONFINT(A480,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-129.394755553826</v>
       </c>
       <c r="E480" s="10">
-        <f>C480+_xlfn.FORECAST.ETS.CONFINT(A480,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>235.37561338334601</v>
       </c>
     </row>
@@ -14562,15 +14657,15 @@
         <v>45406</v>
       </c>
       <c r="C481">
-        <f>_xlfn.FORECAST.ETS(A481,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>71.854010903489794</v>
       </c>
       <c r="D481" s="10">
-        <f>C481-_xlfn.FORECAST.ETS.CONFINT(A481,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-111.32228220842025</v>
       </c>
       <c r="E481" s="10">
-        <f>C481+_xlfn.FORECAST.ETS.CONFINT(A481,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>255.03030401539985</v>
       </c>
     </row>
@@ -14579,15 +14674,15 @@
         <v>45407</v>
       </c>
       <c r="C482">
-        <f>_xlfn.FORECAST.ETS(A482,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>55.564849633599174</v>
       </c>
       <c r="D482" s="10">
-        <f>C482-_xlfn.FORECAST.ETS.CONFINT(A482,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-128.40346292255509</v>
       </c>
       <c r="E482" s="10">
-        <f>C482+_xlfn.FORECAST.ETS.CONFINT(A482,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>239.53316218975345</v>
       </c>
     </row>
@@ -14596,15 +14691,15 @@
         <v>45408</v>
       </c>
       <c r="C483">
-        <f>_xlfn.FORECAST.ETS(A483,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>61.038667459843914</v>
       </c>
       <c r="D483" s="10">
-        <f>C483-_xlfn.FORECAST.ETS.CONFINT(A483,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-123.72257537740745</v>
       </c>
       <c r="E483" s="10">
-        <f>C483+_xlfn.FORECAST.ETS.CONFINT(A483,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>245.79991029709527</v>
       </c>
     </row>
@@ -14613,15 +14708,15 @@
         <v>45409</v>
       </c>
       <c r="C484">
-        <f>_xlfn.FORECAST.ETS(A484,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>27.03603804040609</v>
       </c>
       <c r="D484" s="10">
-        <f>C484-_xlfn.FORECAST.ETS.CONFINT(A484,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-158.51904593670082</v>
       </c>
       <c r="E484" s="10">
-        <f>C484+_xlfn.FORECAST.ETS.CONFINT(A484,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>212.59112201751299</v>
       </c>
     </row>
@@ -14630,15 +14725,15 @@
         <v>45410</v>
       </c>
       <c r="C485">
-        <f>_xlfn.FORECAST.ETS(A485,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>21.955756213246101</v>
       </c>
       <c r="D485" s="10">
-        <f>C485-_xlfn.FORECAST.ETS.CONFINT(A485,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-164.3940797706509</v>
       </c>
       <c r="E485" s="10">
-        <f>C485+_xlfn.FORECAST.ETS.CONFINT(A485,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>208.30559219714311</v>
       </c>
     </row>
@@ -14647,15 +14742,15 @@
         <v>45411</v>
       </c>
       <c r="C486">
-        <f>_xlfn.FORECAST.ETS(A486,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>36.446495546746561</v>
       </c>
       <c r="D486" s="10">
-        <f>C486-_xlfn.FORECAST.ETS.CONFINT(A486,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-152.12895254029439</v>
       </c>
       <c r="E486" s="10">
-        <f>C486+_xlfn.FORECAST.ETS.CONFINT(A486,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>225.02194363378749</v>
       </c>
     </row>
@@ -14664,15 +14759,15 @@
         <v>45412</v>
       </c>
       <c r="C487">
-        <f>_xlfn.FORECAST.ETS(A487,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>52.517238103774474</v>
       </c>
       <c r="D487" s="10">
-        <f>C487-_xlfn.FORECAST.ETS.CONFINT(A487,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-136.84876866673915</v>
       </c>
       <c r="E487" s="10">
-        <f>C487+_xlfn.FORECAST.ETS.CONFINT(A487,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>241.8832448742881</v>
       </c>
     </row>
@@ -14681,15 +14776,15 @@
         <v>45413</v>
       </c>
       <c r="C488">
-        <f>_xlfn.FORECAST.ETS(A488,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>71.380820092504266</v>
       </c>
       <c r="D488" s="10">
-        <f>C488-_xlfn.FORECAST.ETS.CONFINT(A488,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-118.77669958581735</v>
       </c>
       <c r="E488" s="10">
-        <f>C488+_xlfn.FORECAST.ETS.CONFINT(A488,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>261.53833977082587</v>
       </c>
     </row>
@@ -14698,15 +14793,15 @@
         <v>45414</v>
       </c>
       <c r="C489">
-        <f>_xlfn.FORECAST.ETS(A489,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>55.091658822613653</v>
       </c>
       <c r="D489" s="10">
-        <f>C489-_xlfn.FORECAST.ETS.CONFINT(A489,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-135.85832748988022</v>
       </c>
       <c r="E489" s="10">
-        <f>C489+_xlfn.FORECAST.ETS.CONFINT(A489,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>246.04164513510753</v>
       </c>
     </row>
@@ -14715,15 +14810,15 @@
         <v>45415</v>
       </c>
       <c r="C490">
-        <f>_xlfn.FORECAST.ETS(A490,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>60.565476648858393</v>
       </c>
       <c r="D490" s="10">
-        <f>C490-_xlfn.FORECAST.ETS.CONFINT(A490,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-131.17792952019704</v>
       </c>
       <c r="E490" s="10">
-        <f>C490+_xlfn.FORECAST.ETS.CONFINT(A490,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>252.3088828179138</v>
       </c>
     </row>
@@ -14732,15 +14827,15 @@
         <v>45416</v>
       </c>
       <c r="C491">
-        <f>_xlfn.FORECAST.ETS(A491,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>26.562847229420569</v>
       </c>
       <c r="D491" s="10">
-        <f>C491-_xlfn.FORECAST.ETS.CONFINT(A491,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-165.97493150875505</v>
       </c>
       <c r="E491" s="10">
-        <f>C491+_xlfn.FORECAST.ETS.CONFINT(A491,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>219.10062596759616</v>
       </c>
     </row>
@@ -14749,15 +14844,15 @@
         <v>45417</v>
       </c>
       <c r="C492">
-        <f>_xlfn.FORECAST.ETS(A492,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>21.48256540226058</v>
       </c>
       <c r="D492" s="10">
-        <f>C492-_xlfn.FORECAST.ETS.CONFINT(A492,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-171.85053810205321</v>
       </c>
       <c r="E492" s="10">
-        <f>C492+_xlfn.FORECAST.ETS.CONFINT(A492,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>214.81566890657436</v>
       </c>
     </row>
@@ -14766,15 +14861,15 @@
         <v>45418</v>
       </c>
       <c r="C493">
-        <f>_xlfn.FORECAST.ETS(A493,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>35.973304735761033</v>
       </c>
       <c r="D493" s="10">
-        <f>C493-_xlfn.FORECAST.ETS.CONFINT(A493,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-159.55438046928498</v>
       </c>
       <c r="E493" s="10">
-        <f>C493+_xlfn.FORECAST.ETS.CONFINT(A493,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>231.50098994080702</v>
       </c>
     </row>
@@ -14783,15 +14878,15 @@
         <v>45419</v>
       </c>
       <c r="C494">
-        <f>_xlfn.FORECAST.ETS(A494,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="9"/>
         <v>52.04404729278896</v>
       </c>
       <c r="D494" s="10">
-        <f>C494-_xlfn.FORECAST.ETS.CONFINT(A494,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="10"/>
         <v>-144.27518724492114</v>
       </c>
       <c r="E494" s="10">
-        <f>C494+_xlfn.FORECAST.ETS.CONFINT(A494,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="11"/>
         <v>248.36328183049909</v>
       </c>
     </row>
@@ -14800,15 +14895,15 @@
         <v>45420</v>
       </c>
       <c r="C495">
-        <f>_xlfn.FORECAST.ETS(A495,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" ref="C495:C519" si="12">_xlfn.FORECAST.ETS(A495,$B$2:$B$366,$A$2:$A$366,1,1)</f>
         <v>70.907629281518751</v>
       </c>
       <c r="D495" s="10">
-        <f>C495-_xlfn.FORECAST.ETS.CONFINT(A495,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="D495:D519" si="13">C495-_xlfn.FORECAST.ETS.CONFINT(A495,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>-126.20414428589518</v>
       </c>
       <c r="E495" s="10">
-        <f>C495+_xlfn.FORECAST.ETS.CONFINT(A495,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" ref="E495:E519" si="14">C495+_xlfn.FORECAST.ETS.CONFINT(A495,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
         <v>268.01940284893271</v>
       </c>
     </row>
@@ -14817,15 +14912,15 @@
         <v>45421</v>
       </c>
       <c r="C496">
-        <f>_xlfn.FORECAST.ETS(A496,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>54.618468011628131</v>
       </c>
       <c r="D496" s="10">
-        <f>C496-_xlfn.FORECAST.ETS.CONFINT(A496,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-143.28683336105055</v>
       </c>
       <c r="E496" s="10">
-        <f>C496+_xlfn.FORECAST.ETS.CONFINT(A496,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>252.5237693843068</v>
       </c>
     </row>
@@ -14834,15 +14929,15 @@
         <v>45422</v>
       </c>
       <c r="C497">
-        <f>_xlfn.FORECAST.ETS(A497,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>60.092285837872872</v>
       </c>
       <c r="D497" s="10">
-        <f>C497-_xlfn.FORECAST.ETS.CONFINT(A497,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-138.60753119410262</v>
       </c>
       <c r="E497" s="10">
-        <f>C497+_xlfn.FORECAST.ETS.CONFINT(A497,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>258.79210286984835</v>
       </c>
     </row>
@@ -14851,15 +14946,15 @@
         <v>45423</v>
       </c>
       <c r="C498">
-        <f>_xlfn.FORECAST.ETS(A498,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>26.089656418435041</v>
       </c>
       <c r="D498" s="10">
-        <f>C498-_xlfn.FORECAST.ETS.CONFINT(A498,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-173.40566320533679</v>
       </c>
       <c r="E498" s="10">
-        <f>C498+_xlfn.FORECAST.ETS.CONFINT(A498,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>225.58497604220685</v>
       </c>
     </row>
@@ -14868,15 +14963,15 @@
         <v>45424</v>
       </c>
       <c r="C499">
-        <f>_xlfn.FORECAST.ETS(A499,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>21.009374591275058</v>
       </c>
       <c r="D499" s="10">
-        <f>C499-_xlfn.FORECAST.ETS.CONFINT(A499,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-179.28243363530211</v>
       </c>
       <c r="E499" s="10">
-        <f>C499+_xlfn.FORECAST.ETS.CONFINT(A499,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>221.30118281785221</v>
       </c>
     </row>
@@ -14885,15 +14980,15 @@
         <v>45425</v>
       </c>
       <c r="C500">
-        <f>_xlfn.FORECAST.ETS(A500,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>35.500113924775519</v>
       </c>
       <c r="D500" s="10">
-        <f>C500-_xlfn.FORECAST.ETS.CONFINT(A500,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-166.95816935534577</v>
       </c>
       <c r="E500" s="10">
-        <f>C500+_xlfn.FORECAST.ETS.CONFINT(A500,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>237.95839720489681</v>
       </c>
     </row>
@@ -14902,15 +14997,15 @@
         <v>45426</v>
       </c>
       <c r="C501">
-        <f>_xlfn.FORECAST.ETS(A501,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>51.570856481803432</v>
       </c>
       <c r="D501" s="10">
-        <f>C501-_xlfn.FORECAST.ETS.CONFINT(A501,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-151.68050671019779</v>
       </c>
       <c r="E501" s="10">
-        <f>C501+_xlfn.FORECAST.ETS.CONFINT(A501,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>254.82221967380468</v>
       </c>
     </row>
@@ -14919,15 +15014,15 @@
         <v>45427</v>
       </c>
       <c r="C502">
-        <f>_xlfn.FORECAST.ETS(A502,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>70.434438470533223</v>
       </c>
       <c r="D502" s="10">
-        <f>C502-_xlfn.FORECAST.ETS.CONFINT(A502,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-133.61102328306944</v>
       </c>
       <c r="E502" s="10">
-        <f>C502+_xlfn.FORECAST.ETS.CONFINT(A502,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>274.47990022413592</v>
       </c>
     </row>
@@ -14936,15 +15031,15 @@
         <v>45428</v>
       </c>
       <c r="C503">
-        <f>_xlfn.FORECAST.ETS(A503,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>54.145277200642603</v>
       </c>
       <c r="D503" s="10">
-        <f>C503-_xlfn.FORECAST.ETS.CONFINT(A503,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-150.69530051467817</v>
       </c>
       <c r="E503" s="10">
-        <f>C503+_xlfn.FORECAST.ETS.CONFINT(A503,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>258.98585491596339</v>
       </c>
     </row>
@@ -14953,15 +15048,15 @@
         <v>45429</v>
       </c>
       <c r="C504">
-        <f>_xlfn.FORECAST.ETS(A504,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>59.619095026887344</v>
       </c>
       <c r="D504" s="10">
-        <f>C504-_xlfn.FORECAST.ETS.CONFINT(A504,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-146.0176148048771</v>
       </c>
       <c r="E504" s="10">
-        <f>C504+_xlfn.FORECAST.ETS.CONFINT(A504,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>265.2558048586518</v>
       </c>
     </row>
@@ -14970,15 +15065,15 @@
         <v>45430</v>
       </c>
       <c r="C505">
-        <f>_xlfn.FORECAST.ETS(A505,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>25.61646560744952</v>
       </c>
       <c r="D505" s="10">
-        <f>C505-_xlfn.FORECAST.ETS.CONFINT(A505,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-180.81739125428663</v>
       </c>
       <c r="E505" s="10">
-        <f>C505+_xlfn.FORECAST.ETS.CONFINT(A505,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>232.05032246918569</v>
       </c>
     </row>
@@ -14987,15 +15082,15 @@
         <v>45431</v>
       </c>
       <c r="C506">
-        <f>_xlfn.FORECAST.ETS(A506,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>20.53618378028953</v>
       </c>
       <c r="D506" s="10">
-        <f>C506-_xlfn.FORECAST.ETS.CONFINT(A506,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-186.69583378792325</v>
       </c>
       <c r="E506" s="10">
-        <f>C506+_xlfn.FORECAST.ETS.CONFINT(A506,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>227.76820134850229</v>
       </c>
     </row>
@@ -15004,15 +15099,15 @@
         <v>45432</v>
       </c>
       <c r="C507">
-        <f>_xlfn.FORECAST.ETS(A507,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>35.026923113789991</v>
       </c>
       <c r="D507" s="10">
-        <f>C507-_xlfn.FORECAST.ETS.CONFINT(A507,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-174.34602432803948</v>
       </c>
       <c r="E507" s="10">
-        <f>C507+_xlfn.FORECAST.ETS.CONFINT(A507,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>244.39987055561946</v>
       </c>
     </row>
@@ -15021,15 +15116,15 @@
         <v>45433</v>
       </c>
       <c r="C508">
-        <f>_xlfn.FORECAST.ETS(A508,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>51.097665670817904</v>
       </c>
       <c r="D508" s="10">
-        <f>C508-_xlfn.FORECAST.ETS.CONFINT(A508,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-159.07035765336258</v>
       </c>
       <c r="E508" s="10">
-        <f>C508+_xlfn.FORECAST.ETS.CONFINT(A508,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>261.26568899499841</v>
       </c>
     </row>
@@ -15038,15 +15133,15 @@
         <v>45434</v>
       </c>
       <c r="C509">
-        <f>_xlfn.FORECAST.ETS(A509,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>69.961247659547695</v>
       </c>
       <c r="D509" s="10">
-        <f>C509-_xlfn.FORECAST.ETS.CONFINT(A509,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-141.00289379164693</v>
       </c>
       <c r="E509" s="10">
-        <f>C509+_xlfn.FORECAST.ETS.CONFINT(A509,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>280.92538911074234</v>
       </c>
     </row>
@@ -15055,15 +15150,15 @@
         <v>45435</v>
       </c>
       <c r="C510">
-        <f>_xlfn.FORECAST.ETS(A510,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>53.672086389657082</v>
       </c>
       <c r="D510" s="10">
-        <f>C510-_xlfn.FORECAST.ETS.CONFINT(A510,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-158.08921392918865</v>
       </c>
       <c r="E510" s="10">
-        <f>C510+_xlfn.FORECAST.ETS.CONFINT(A510,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>265.43338670850278</v>
       </c>
     </row>
@@ -15072,15 +15167,15 @@
         <v>45436</v>
       </c>
       <c r="C511">
-        <f>_xlfn.FORECAST.ETS(A511,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>59.145904215901822</v>
       </c>
       <c r="D511" s="10">
-        <f>C511-_xlfn.FORECAST.ETS.CONFINT(A511,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-153.413594214466</v>
       </c>
       <c r="E511" s="10">
-        <f>C511+_xlfn.FORECAST.ETS.CONFINT(A511,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>271.70540264626965</v>
       </c>
     </row>
@@ -15089,15 +15184,15 @@
         <v>45437</v>
       </c>
       <c r="C512">
-        <f>_xlfn.FORECAST.ETS(A512,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>25.143274796463999</v>
       </c>
       <c r="D512" s="10">
-        <f>C512-_xlfn.FORECAST.ETS.CONFINT(A512,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-188.21545949972869</v>
       </c>
       <c r="E512" s="10">
-        <f>C512+_xlfn.FORECAST.ETS.CONFINT(A512,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>238.50200909265669</v>
       </c>
     </row>
@@ -15106,15 +15201,15 @@
         <v>45438</v>
       </c>
       <c r="C513">
-        <f>_xlfn.FORECAST.ETS(A513,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>20.062992969304009</v>
       </c>
       <c r="D513" s="10">
-        <f>C513-_xlfn.FORECAST.ETS.CONFINT(A513,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-194.09601346458359</v>
       </c>
       <c r="E513" s="10">
-        <f>C513+_xlfn.FORECAST.ETS.CONFINT(A513,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>234.22199940319163</v>
       </c>
     </row>
@@ -15123,15 +15218,15 @@
         <v>45439</v>
       </c>
       <c r="C514">
-        <f>_xlfn.FORECAST.ETS(A514,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>34.553732302804463</v>
       </c>
       <c r="D514" s="10">
-        <f>C514-_xlfn.FORECAST.ETS.CONFINT(A514,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-181.7229164017177</v>
       </c>
       <c r="E514" s="10">
-        <f>C514+_xlfn.FORECAST.ETS.CONFINT(A514,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>250.83038100732662</v>
       </c>
     </row>
@@ -15140,15 +15235,15 @@
         <v>45440</v>
       </c>
       <c r="C515">
-        <f>_xlfn.FORECAST.ETS(A515,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>50.624474859832389</v>
       </c>
       <c r="D515" s="10">
-        <f>C515-_xlfn.FORECAST.ETS.CONFINT(A515,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-166.44964877818174</v>
       </c>
       <c r="E515" s="10">
-        <f>C515+_xlfn.FORECAST.ETS.CONFINT(A515,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>267.69859849784655</v>
       </c>
     </row>
@@ -15157,15 +15252,15 @@
         <v>45441</v>
       </c>
       <c r="C516">
-        <f>_xlfn.FORECAST.ETS(A516,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>69.488056848562181</v>
       </c>
       <c r="D516" s="10">
-        <f>C516-_xlfn.FORECAST.ETS.CONFINT(A516,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-148.38460312709327</v>
       </c>
       <c r="E516" s="10">
-        <f>C516+_xlfn.FORECAST.ETS.CONFINT(A516,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>287.36071682421766</v>
       </c>
     </row>
@@ -15174,15 +15269,15 @@
         <v>45442</v>
       </c>
       <c r="C517">
-        <f>_xlfn.FORECAST.ETS(A517,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>53.198895578671561</v>
       </c>
       <c r="D517" s="10">
-        <f>C517-_xlfn.FORECAST.ETS.CONFINT(A517,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-165.47336043780783</v>
       </c>
       <c r="E517" s="10">
-        <f>C517+_xlfn.FORECAST.ETS.CONFINT(A517,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>271.87115159515093</v>
       </c>
     </row>
@@ -15191,15 +15286,15 @@
         <v>45443</v>
       </c>
       <c r="C518">
-        <f>_xlfn.FORECAST.ETS(A518,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>58.672713404916301</v>
       </c>
       <c r="D518" s="10">
-        <f>C518-_xlfn.FORECAST.ETS.CONFINT(A518,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-160.80019666402436</v>
       </c>
       <c r="E518" s="10">
-        <f>C518+_xlfn.FORECAST.ETS.CONFINT(A518,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>278.14562347385697</v>
       </c>
     </row>
@@ -15208,15 +15303,15 @@
         <v>45444</v>
       </c>
       <c r="C519">
-        <f>_xlfn.FORECAST.ETS(A519,$B$2:$B$366,$A$2:$A$366,1,1)</f>
+        <f t="shared" si="12"/>
         <v>24.67008398547847</v>
       </c>
       <c r="D519" s="10">
-        <f>C519-_xlfn.FORECAST.ETS.CONFINT(A519,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="13"/>
         <v>-195.60453646534776</v>
       </c>
       <c r="E519" s="10">
-        <f>C519+_xlfn.FORECAST.ETS.CONFINT(A519,$B$2:$B$366,$A$2:$A$366,0.95,1,1)</f>
+        <f t="shared" si="14"/>
         <v>244.9447044363047</v>
       </c>
     </row>
@@ -18171,225 +18266,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB0B52F-243B-4FED-BD7E-2E9F6BB7D9BF}">
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2.28515625" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="67"/>
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="67" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" collapsed="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="69" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="69" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="69" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="69" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="68" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="68" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="71">
-        <v>640000.00000003458</v>
-      </c>
-      <c r="E16" s="71">
-        <v>640000.00000003458</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="69" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="69" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="69" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="70" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="72">
-        <v>0.1</v>
-      </c>
-      <c r="E21" s="72">
-        <v>0.1</v>
-      </c>
-      <c r="F21" s="70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="68" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="68" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="73">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E22" s="73">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="F22" s="68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="69" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="69" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="69" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26" s="69" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="68" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="68" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="71">
-        <v>640000.00000003458</v>
-      </c>
-      <c r="E27" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="68" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="68">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2F967B-A46A-4D9A-B93E-099143C21106}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.85546875" customWidth="1"/>
@@ -18407,11 +18285,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="58"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="57"/>
       <c r="D1" s="11" t="s">
         <v>7</v>
       </c>
@@ -18424,23 +18302,17 @@
       <c r="G1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="60" t="s">
+      <c r="I1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="61"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="J1" s="79"/>
+      <c r="K1" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="81"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -18449,7 +18321,7 @@
       <c r="B2" s="36">
         <v>100000</v>
       </c>
-      <c r="C2" s="58"/>
+      <c r="C2" s="57"/>
       <c r="D2" s="15" t="s">
         <v>25</v>
       </c>
@@ -18465,22 +18337,14 @@
       <c r="I2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="64">
+      <c r="J2" s="59">
         <v>100000</v>
       </c>
-      <c r="K2" s="62"/>
-      <c r="L2" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="16">
-        <v>100000</v>
-      </c>
-      <c r="N2" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="O2" s="18">
-        <v>1.4999999999999999E-2</v>
-      </c>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -18489,7 +18353,7 @@
       <c r="B3" s="37">
         <v>0.1</v>
       </c>
-      <c r="C3" s="58"/>
+      <c r="C3" s="57"/>
       <c r="D3" s="15" t="s">
         <v>26</v>
       </c>
@@ -18505,22 +18369,14 @@
       <c r="I3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="65">
-        <v>0.1</v>
-      </c>
-      <c r="K3" s="62"/>
-      <c r="L3" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="16">
-        <v>80000</v>
-      </c>
-      <c r="N3" s="17">
-        <v>0.15</v>
-      </c>
-      <c r="O3" s="18">
-        <v>1.2E-2</v>
-      </c>
+      <c r="J3" s="60">
+        <v>0.12295418126546183</v>
+      </c>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
@@ -18529,7 +18385,7 @@
       <c r="B4" s="38">
         <v>7.5844363108327748E-2</v>
       </c>
-      <c r="C4" s="58"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="20" t="s">
         <v>27</v>
       </c>
@@ -18545,27 +18401,21 @@
       <c r="I4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="66">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="K4" s="62"/>
-      <c r="L4" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="21">
-        <v>120000</v>
-      </c>
-      <c r="N4" s="22">
-        <v>0.05</v>
-      </c>
-      <c r="O4" s="23">
-        <v>8.0000000000000002E-3</v>
-      </c>
+      <c r="J4" s="61">
+        <v>6.5493586951151372E-2</v>
+      </c>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="58"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
       <c r="D5" s="24" t="s">
         <v>11</v>
       </c>
@@ -18579,42 +18429,33 @@
       <c r="G5" s="27">
         <v>0.04</v>
       </c>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="25" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N5" s="26">
-        <v>0.25</v>
-      </c>
-      <c r="O5" s="27">
-        <v>0.04</v>
-      </c>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
     </row>
     <row r="6" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="I6" s="60" t="s">
+      <c r="B6" s="79"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="I6" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
@@ -18623,22 +18464,22 @@
       <c r="B7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
       <c r="I7" s="28" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="62"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="62"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="58"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="30">
@@ -18648,27 +18489,25 @@
         <f>(base*(1+raise)^A8)*(1+bonus)</f>
         <v>110000.00000000001</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="59" t="s">
+      <c r="C8" s="57"/>
+      <c r="D8" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
       <c r="I8" s="30">
         <v>0</v>
       </c>
       <c r="J8" s="31">
-        <f>(base*(1+raise)^I8)*(1+bonus)</f>
-        <v>110000.00000000001</v>
-      </c>
-      <c r="K8" s="62"/>
-      <c r="L8" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="63"/>
-      <c r="N8" s="62"/>
-      <c r="O8" s="62"/>
+        <f>(base2*(1+raise2)^I8)*(1+bonus2)</f>
+        <v>112295.41812654618</v>
+      </c>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+      <c r="O8" s="58"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="30">
@@ -18678,23 +18517,23 @@
         <f>(base*(1+raise)^A9)*(1+bonus)</f>
         <v>118342.87994191605</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
       <c r="I9" s="30">
         <v>1</v>
       </c>
       <c r="J9" s="31">
-        <f>(base*(1+raise)^I9)*(1+bonus)</f>
-        <v>118342.87994191605</v>
-      </c>
-      <c r="K9" s="62"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="62"/>
-      <c r="O9" s="62"/>
+        <f>(base2*(1+raise2)^I9)*(1+bonus2)</f>
+        <v>119650.04785783301</v>
+      </c>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="30">
@@ -18704,23 +18543,23 @@
         <f>(base*(1+raise)^A10)*(1+bonus)</f>
         <v>127318.52029951598</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
       <c r="I10" s="30">
         <v>2</v>
       </c>
       <c r="J10" s="31">
-        <f>(base*(1+raise)^I10)*(1+bonus)</f>
-        <v>127318.52029951598</v>
-      </c>
-      <c r="K10" s="62"/>
-      <c r="L10" s="62"/>
-      <c r="M10" s="62"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="62"/>
+        <f>(base2*(1+raise2)^I10)*(1+bonus2)</f>
+        <v>127486.35867091942</v>
+      </c>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="58"/>
+      <c r="N10" s="58"/>
+      <c r="O10" s="58"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="30">
@@ -18730,23 +18569,25 @@
         <f>(base*(1+raise)^A11)*(1+bonus)</f>
         <v>136974.91238352744</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
       <c r="I11" s="30">
         <v>3</v>
       </c>
       <c r="J11" s="31">
-        <f>(base*(1+raise)^I11)*(1+bonus)</f>
-        <v>136974.91238352744</v>
-      </c>
-      <c r="K11" s="62"/>
-      <c r="L11" s="62"/>
-      <c r="M11" s="62"/>
-      <c r="N11" s="62"/>
-      <c r="O11" s="62"/>
+        <f>(base2*(1+raise2)^I11)*(1+bonus2)</f>
+        <v>135835.89758761897</v>
+      </c>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="58"/>
+      <c r="O11" s="58"/>
     </row>
     <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="32">
@@ -18756,23 +18597,23 @@
         <f>(base*(1+raise)^A12)*(1+bonus)</f>
         <v>147363.6873750751</v>
       </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
       <c r="I12" s="32">
         <v>4</v>
       </c>
-      <c r="J12" s="33">
-        <f>(base*(1+raise)^I12)*(1+bonus)</f>
-        <v>147363.6873750751</v>
-      </c>
-      <c r="K12" s="62"/>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="62"/>
+      <c r="J12" s="31">
+        <f>(base2*(1+raise2)^I12)*(1+bonus2)</f>
+        <v>144732.27775736136</v>
+      </c>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
     </row>
     <row r="13" spans="1:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
@@ -18782,48 +18623,223 @@
         <f>SUM(B8:B12)</f>
         <v>640000.00000003458</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
       <c r="I13" s="34" t="s">
         <v>15</v>
       </c>
       <c r="J13" s="35">
         <f>SUM(J8:J12)</f>
-        <v>640000.00000003458</v>
-      </c>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="62"/>
+        <v>640000.00000027893</v>
+      </c>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="58"/>
+      <c r="O13" s="58"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="79"/>
+      <c r="C15" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="80"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="72">
+        <v>100000</v>
+      </c>
+      <c r="C16" s="80"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="74">
+        <v>0.11</v>
+      </c>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="75">
+        <v>7.1307883172034958E-2</v>
+      </c>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="73"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="78" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="79"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="30">
+        <v>0</v>
+      </c>
+      <c r="B22" s="31">
+        <f>(base3*(1+raise3)^A22)*(1+bonus3)</f>
+        <v>111000.00000000001</v>
+      </c>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="30">
+        <v>1</v>
+      </c>
+      <c r="B23" s="31">
+        <f>(base3*(1+raise3)^A23)*(1+bonus3)</f>
+        <v>118915.1750320959</v>
+      </c>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="30">
+        <v>2</v>
+      </c>
+      <c r="B24" s="31">
+        <f>(base3*(1+raise3)^A24)*(1+bonus3)</f>
+        <v>127394.76444066671</v>
+      </c>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="30">
+        <v>3</v>
+      </c>
+      <c r="B25" s="31">
+        <f>(base3*(1+raise3)^A25)*(1+bonus3)</f>
+        <v>136479.01542013069</v>
+      </c>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="32">
+        <v>4</v>
+      </c>
+      <c r="B26" s="31">
+        <f>(base3*(1+raise3)^A26)*(1+bonus3)</f>
+        <v>146211.04510714373</v>
+      </c>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="35">
+        <f>SUM(B22:B26)</f>
+        <v>640000.00000003702</v>
+      </c>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
     </row>
   </sheetData>
   <scenarios current="0" show="0" sqref="C9:C14">
     <scenario name="Job A" locked="1" count="3" user="Animesh Karmakar" comment="Created by Animesh Karmakar on 04-10-2026">
-      <inputCells r="B2" val="100000" numFmtId="168"/>
+      <inputCells r="B2" val="100000" numFmtId="165"/>
       <inputCells r="B3" val="0.1" numFmtId="9"/>
-      <inputCells r="B4" val="0.015" numFmtId="169"/>
+      <inputCells r="B4" val="0.015" numFmtId="166"/>
     </scenario>
     <scenario name="Job B" locked="1" count="3" user="Animesh Karmakar" comment="Created by Animesh Karmakar on 04-10-2026_x000a_Modified by Animesh Karmakar on 04-10-2026">
-      <inputCells r="B2" val="80000" numFmtId="168"/>
+      <inputCells r="B2" val="80000" numFmtId="165"/>
       <inputCells r="B3" val="0.15" numFmtId="9"/>
-      <inputCells r="B4" val="0.012" numFmtId="169"/>
+      <inputCells r="B4" val="0.012" numFmtId="166"/>
     </scenario>
     <scenario name="Job C" locked="1" count="3" user="Animesh Karmakar" comment="Created by Animesh Karmakar on 04-10-2026">
-      <inputCells r="B2" val="120000" numFmtId="168"/>
+      <inputCells r="B2" val="120000" numFmtId="165"/>
       <inputCells r="B3" val="0.05" numFmtId="9"/>
-      <inputCells r="B4" val="0.008" numFmtId="169"/>
+      <inputCells r="B4" val="0.008" numFmtId="166"/>
     </scenario>
     <scenario name="1" count="2" user="Animesh Karmakar" comment="Created by Animesh Karmakar on 10/4/2026">
       <inputCells r="J3" val="0.1" numFmtId="9"/>
-      <inputCells r="J4" val="0.015" numFmtId="169"/>
+      <inputCells r="J4" val="0.015" numFmtId="166"/>
     </scenario>
   </scenarios>
-  <mergeCells count="6">
-    <mergeCell ref="L8:M9"/>
+  <mergeCells count="9">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="K1:L2"/>
     <mergeCell ref="D8:E9"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:B6"/>
@@ -18834,7 +18850,481 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA81AE92-88CC-435A-AD01-FA7FC37F545C}">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="62" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="62" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="62" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="62"/>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="62"/>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="62"/>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="62" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" collapsed="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="76">
+        <v>640000.00000027893</v>
+      </c>
+      <c r="E16" s="76">
+        <v>640000.00000003702</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="66">
+        <v>0.12295418126546183</v>
+      </c>
+      <c r="E21" s="66">
+        <v>0.11</v>
+      </c>
+      <c r="F21" s="65" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="67">
+        <v>6.5493586951151372E-2</v>
+      </c>
+      <c r="E22" s="67">
+        <v>7.1307883172034958E-2</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="64" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="64" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="77">
+        <v>640000.00000003702</v>
+      </c>
+      <c r="E27" s="65" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="66">
+        <v>0.11</v>
+      </c>
+      <c r="E28" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="67">
+        <v>7.1307883172034958E-2</v>
+      </c>
+      <c r="E29" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" s="63">
+        <v>2.8692116827965047E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE767F19-3B78-4F4A-B5F5-F839D371F432}">
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="62" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="62" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="62" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="62"/>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="62"/>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="62"/>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="62" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" collapsed="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="70">
+        <v>566749.36181874992</v>
+      </c>
+      <c r="E16" s="70">
+        <v>640000.00000027893</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="66">
+        <v>0.1</v>
+      </c>
+      <c r="E21" s="66">
+        <v>0.12295418126546183</v>
+      </c>
+      <c r="F21" s="65" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="67">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E22" s="67">
+        <v>6.5493586951151372E-2</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="64" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="64" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="70">
+        <v>640000.00000027893</v>
+      </c>
+      <c r="E27" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="63">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4681C28-6458-4DB9-9127-E4472D0D6EBF}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -18844,231 +19334,230 @@
   <cols>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="19.140625" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="26.7109375" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="24" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
     </row>
     <row r="3" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="48" t="s">
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="F3" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="71" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="33" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="50" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="E4" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="49" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
     </row>
     <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="44"/>
-      <c r="C6" s="44" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="50">
         <v>120000</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="52">
         <v>100000</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6" s="52">
         <v>80000</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="52">
         <v>120000</v>
       </c>
     </row>
     <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="44"/>
-      <c r="C7" s="44" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="51">
         <v>0.05</v>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="53">
         <v>0.1</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="53">
         <v>0.15</v>
       </c>
-      <c r="G7" s="54">
+      <c r="G7" s="53">
         <v>0.05</v>
       </c>
     </row>
     <row r="8" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="44"/>
-      <c r="C8" s="44" t="s">
+      <c r="B8" s="43"/>
+      <c r="C8" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="39">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="48">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="48">
         <v>1.2E-2</v>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="48">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
     </row>
     <row r="10" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="44"/>
-      <c r="C10" s="44" t="s">
+      <c r="B10" s="43"/>
+      <c r="C10" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="50">
         <v>126000</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="50">
         <v>110000</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="50">
         <v>92000</v>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="50">
         <v>126000</v>
       </c>
     </row>
     <row r="11" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="44"/>
-      <c r="C11" s="44" t="s">
+      <c r="B11" s="43"/>
+      <c r="C11" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="50">
         <v>127008</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="50">
         <v>111650</v>
       </c>
-      <c r="F11" s="51">
+      <c r="F11" s="50">
         <v>93104</v>
       </c>
-      <c r="G11" s="51">
+      <c r="G11" s="50">
         <v>127008</v>
       </c>
     </row>
     <row r="12" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="44"/>
-      <c r="C12" s="44" t="s">
+      <c r="B12" s="43"/>
+      <c r="C12" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <v>128024.064</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="50">
         <v>113324.75</v>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="50">
         <v>94221.248000000007</v>
       </c>
-      <c r="G12" s="51">
+      <c r="G12" s="50">
         <v>128024.064</v>
       </c>
     </row>
     <row r="13" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="44"/>
-      <c r="C13" s="44" t="s">
+      <c r="B13" s="43"/>
+      <c r="C13" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="50">
         <v>129048.25651200001</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="50">
         <v>115024.62125</v>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="50">
         <v>95351.902975999998</v>
       </c>
-      <c r="G13" s="51">
+      <c r="G13" s="50">
         <v>129048.25651200001</v>
       </c>
     </row>
     <row r="14" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56" t="s">
+      <c r="B14" s="55"/>
+      <c r="C14" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="56">
         <v>130080.64256409599</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="56">
         <v>116749.99056875</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="56">
         <v>96496.125811712001</v>
       </c>
-      <c r="G14" s="57">
+      <c r="G14" s="56">
         <v>130080.64256409599</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="46"/>
-      <c r="C15" s="46" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="54">
         <v>640160.96307609603</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="54">
         <v>566749.36181875004</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="54">
         <v>471173.27678771201</v>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="54">
         <v>640160.96307609603</v>
       </c>
     </row>
